--- a/manuscript/supplementary/Supplementary_tables.xlsx
+++ b/manuscript/supplementary/Supplementary_tables.xlsx
@@ -1398,7 +1398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1409,12 +1409,15 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="90" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supplementary Table 2. The 30 directed synergistic feature pairs with the highest mean total 2D information gain (IG) across the taxa-only, functions-only and combined analyses. base_IG_1D_mean: 1D IG of the base feature; total_IG_2D_mean: joint IG of the pair (base 1D IG + IG added by the contributing feature); ig_difference_raw / ig_difference_pct: absolute and relative gain over the base feature; pair_ig_count: number of fold-run combinations (of 140 = 14 LOCO folds x 10 MDFS runs) in which the pair was among the top 2 % of pairs.</t>
+          <t>Supplementary Table 2. The 30 directed synergistic feature pairs with the highest mean total 2D information gain (IG) across the taxa-only, functions-only and combined analyses. base_IG_1D_mean: 1D IG of the base feature; total_IG_2D_mean: joint IG of the pair (base 1D IG + IG added by the contributing feature); ig_difference_raw / ig_difference_pct: absolute and relative gain over the base feature; pair_ig_count: number of fold-run combinations (of 140 = 14 LOCO folds x 10 MDFS runs) in which the pair was among the top 2 % of pairs. interaction_information_mean: total IG of the pair minus the two individual IGs, averaged over the fold-runs in which the pair was selected; pct_fold_runs_super_additive: share of those fold-runs in which it exceeded the chance threshold obtained by within-class shuffling of the features; super_additive: that share is at least 50 %.</t>
         </is>
       </c>
     </row>
@@ -1459,6 +1462,21 @@
           <t>pair_ig_count</t>
         </is>
       </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>interaction_information_mean</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>pct_fold_runs_super_additive</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>super_additive</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1493,6 +1511,17 @@
           <t>140/140</t>
         </is>
       </c>
+      <c r="I4" t="n">
+        <v>-193.65</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1527,6 +1556,17 @@
           <t>140/140</t>
         </is>
       </c>
+      <c r="I5" t="n">
+        <v>-193.65</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1561,6 +1601,17 @@
           <t>140/140</t>
         </is>
       </c>
+      <c r="I6" t="n">
+        <v>-192.81</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1595,6 +1646,17 @@
           <t>140/140</t>
         </is>
       </c>
+      <c r="I7" t="n">
+        <v>-192.81</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1629,6 +1691,17 @@
           <t>140/140</t>
         </is>
       </c>
+      <c r="I8" t="n">
+        <v>-214.06</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1663,6 +1736,17 @@
           <t>140/140</t>
         </is>
       </c>
+      <c r="I9" t="n">
+        <v>-214.06</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1697,6 +1781,17 @@
           <t>140/140</t>
         </is>
       </c>
+      <c r="I10" t="n">
+        <v>-214.03</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1731,6 +1826,17 @@
           <t>140/140</t>
         </is>
       </c>
+      <c r="I11" t="n">
+        <v>-214.03</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1765,6 +1871,17 @@
           <t>140/140</t>
         </is>
       </c>
+      <c r="I12" t="n">
+        <v>-196.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1799,6 +1916,17 @@
           <t>140/140</t>
         </is>
       </c>
+      <c r="I13" t="n">
+        <v>-196.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1833,6 +1961,17 @@
           <t>140/140</t>
         </is>
       </c>
+      <c r="I14" t="n">
+        <v>-189.78</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1867,6 +2006,17 @@
           <t>140/140</t>
         </is>
       </c>
+      <c r="I15" t="n">
+        <v>-189.78</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1901,6 +2051,17 @@
           <t>134/140</t>
         </is>
       </c>
+      <c r="I16" t="n">
+        <v>-76.81999999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1935,6 +2096,17 @@
           <t>134/140</t>
         </is>
       </c>
+      <c r="I17" t="n">
+        <v>-76.81999999999999</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1969,6 +2141,17 @@
           <t>140/140</t>
         </is>
       </c>
+      <c r="I18" t="n">
+        <v>-76.77</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2003,6 +2186,17 @@
           <t>140/140</t>
         </is>
       </c>
+      <c r="I19" t="n">
+        <v>-76.77</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2037,6 +2231,17 @@
           <t>138/140</t>
         </is>
       </c>
+      <c r="I20" t="n">
+        <v>-180.26</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2071,6 +2276,17 @@
           <t>138/140</t>
         </is>
       </c>
+      <c r="I21" t="n">
+        <v>-180.26</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2105,6 +2321,17 @@
           <t>9/140</t>
         </is>
       </c>
+      <c r="I22" t="n">
+        <v>-32.85</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2139,6 +2366,17 @@
           <t>9/140</t>
         </is>
       </c>
+      <c r="I23" t="n">
+        <v>-32.85</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2173,6 +2411,17 @@
           <t>10/140</t>
         </is>
       </c>
+      <c r="I24" t="n">
+        <v>-32.08</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2207,6 +2456,17 @@
           <t>10/140</t>
         </is>
       </c>
+      <c r="I25" t="n">
+        <v>-32.08</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2241,6 +2501,17 @@
           <t>140/140</t>
         </is>
       </c>
+      <c r="I26" t="n">
+        <v>-177.73</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2275,6 +2546,17 @@
           <t>140/140</t>
         </is>
       </c>
+      <c r="I27" t="n">
+        <v>-177.73</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2309,6 +2591,17 @@
           <t>134/140</t>
         </is>
       </c>
+      <c r="I28" t="n">
+        <v>-166.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2343,6 +2636,17 @@
           <t>134/140</t>
         </is>
       </c>
+      <c r="I29" t="n">
+        <v>-166.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2377,6 +2681,17 @@
           <t>9/140</t>
         </is>
       </c>
+      <c r="I30" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2411,6 +2726,17 @@
           <t>9/140</t>
         </is>
       </c>
+      <c r="I31" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2445,6 +2771,17 @@
           <t>140/140</t>
         </is>
       </c>
+      <c r="I32" t="n">
+        <v>-165.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2477,6 +2814,17 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>140/140</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>-165.6</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2885,7 +3233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M238"/>
+  <dimension ref="A1:P238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2901,12 +3249,15 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="90" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supplementary Table 4. Stable synthetic feature pairs in the CRC data: pairs whose synthetic feature was selected by the final random forest in &gt;= 80 % of the 14 LOCO folds and more often than either constituent (Selection % Gain = pair frequency minus the mean frequency of its constituents). Post-selection effect-size summary per pair: transformation evaluated in most cohorts, number of two-class cohorts, Benjamini-Hochberg q of the Stouffer meta p-value across cohorts, median rank-biserial correlation (positive = higher in CRC) and the number of cohorts with positive / negative direction.</t>
+          <t>Supplementary Table 4. Stable synthetic feature pairs in the CRC data: pairs whose synthetic feature was selected by the final random forest in &gt;= 80 % of the 14 LOCO folds and more often than either constituent (Selection % Gain = pair frequency minus the mean frequency of its constituents). Post-selection effect-size summary per pair: transformation evaluated in most cohorts, number of two-class cohorts, Benjamini-Hochberg q of the Stouffer meta p-value across cohorts, median rank-biserial correlation (positive = higher in CRC) and the number of cohorts with positive / negative direction. interaction_information_mean: total IG of the pair minus the two individual IGs, averaged over the fold-runs in which the pair was selected; pct_fold_runs_super_additive: share of those fold-runs in which it exceeded the chance threshold obtained by within-class shuffling of the features; super_additive: that share is at least 50 %.</t>
         </is>
       </c>
     </row>
@@ -2976,6 +3327,21 @@
           <t>Direction (+CRC/-CRC)</t>
         </is>
       </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>interaction_information_mean</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>pct_fold_runs_super_additive</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>super_additive</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3027,6 +3393,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N4" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="O4" t="n">
+        <v>100</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3078,6 +3455,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N5" t="n">
+        <v>-36.4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3129,6 +3517,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N6" t="n">
+        <v>-177.48</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3180,6 +3579,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N7" t="n">
+        <v>-220.18</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3231,6 +3641,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N8" t="n">
+        <v>-177.73</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3282,6 +3703,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N9" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3333,6 +3765,17 @@
           <t>+2/-13</t>
         </is>
       </c>
+      <c r="N10" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3374,7 +3817,7 @@
         <v>15</v>
       </c>
       <c r="K11" t="n">
-        <v>1.761188411635734e-41</v>
+        <v>1.761188411635733e-41</v>
       </c>
       <c r="L11" t="n">
         <v>-0.4112615823235923</v>
@@ -3384,6 +3827,17 @@
           <t>+1/-14</t>
         </is>
       </c>
+      <c r="N11" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="O11" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3435,6 +3889,17 @@
           <t>+1/-14</t>
         </is>
       </c>
+      <c r="N12" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="O12" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3486,6 +3951,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N13" t="n">
+        <v>-17.24</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3537,6 +4013,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N14" t="n">
+        <v>-28.38</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3588,6 +4075,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N15" t="n">
+        <v>-193.65</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3639,6 +4137,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N16" t="n">
+        <v>-57.45</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3690,6 +4199,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N17" t="n">
+        <v>-20.07</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3741,6 +4261,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N18" t="n">
+        <v>-11.33</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3792,6 +4323,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N19" t="n">
+        <v>-53.27</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3843,6 +4385,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N20" t="n">
+        <v>-12.31</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3894,6 +4447,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N21" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3945,6 +4509,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N22" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="O22" t="n">
+        <v>100</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3996,6 +4571,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N23" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="O23" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4047,6 +4633,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N24" t="n">
+        <v>-50.51</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4098,6 +4695,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N25" t="n">
+        <v>-165.6</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4149,6 +4757,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N26" t="n">
+        <v>-214.06</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4200,6 +4819,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N27" t="n">
+        <v>-196.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4251,6 +4881,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N28" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4302,6 +4943,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N29" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4353,6 +5005,17 @@
           <t>+0/-15</t>
         </is>
       </c>
+      <c r="N30" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="O30" t="n">
+        <v>97.73999999999999</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4404,6 +5067,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N31" t="n">
+        <v>-5.68</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4455,6 +5129,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N32" t="n">
+        <v>-50.07</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4506,6 +5191,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N33" t="n">
+        <v>-7.33</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4557,6 +5253,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N34" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4608,6 +5315,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N35" t="n">
+        <v>-38.42</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4659,6 +5377,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N36" t="n">
+        <v>-4.94</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4710,6 +5439,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N37" t="n">
+        <v>-10.03</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4761,6 +5501,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N38" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4812,6 +5563,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N39" t="n">
+        <v>-37.47</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4863,6 +5625,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N40" t="n">
+        <v>-8.42</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4914,6 +5687,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N41" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4965,6 +5749,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N42" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5016,6 +5811,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N43" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5067,6 +5873,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N44" t="n">
+        <v>-13.59</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5118,6 +5935,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N45" t="n">
+        <v>-10.48</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5169,6 +5997,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N46" t="n">
+        <v>-16.01</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5220,6 +6059,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N47" t="n">
+        <v>-3.54</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5271,6 +6121,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N48" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="O48" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5322,6 +6183,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N49" t="n">
+        <v>-42.19</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5373,6 +6245,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N50" t="n">
+        <v>-10.57</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5424,6 +6307,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N51" t="n">
+        <v>-4.43</v>
+      </c>
+      <c r="O51" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5475,6 +6369,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N52" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5526,6 +6431,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N53" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5577,6 +6493,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N54" t="n">
+        <v>-5.02</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5628,6 +6555,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N55" t="n">
+        <v>-10.53</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5679,6 +6617,17 @@
           <t>+13/-2</t>
         </is>
       </c>
+      <c r="N56" t="n">
+        <v>-10.18</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5730,6 +6679,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N57" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5771,7 +6731,7 @@
         <v>15</v>
       </c>
       <c r="K58" t="n">
-        <v>4.406298448788378e-44</v>
+        <v>4.406298448788379e-44</v>
       </c>
       <c r="L58" t="n">
         <v>0.3879882092851878</v>
@@ -5781,6 +6741,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N58" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="O58" t="n">
+        <v>87.22</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5832,6 +6803,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N59" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="O59" t="n">
+        <v>93.23</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5883,6 +6865,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N60" t="n">
+        <v>-30.83</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5934,6 +6927,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N61" t="n">
+        <v>-63.99</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5985,6 +6989,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N62" t="n">
+        <v>-72.54000000000001</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6036,6 +7051,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N63" t="n">
+        <v>-58.67</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6087,6 +7113,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N64" t="n">
+        <v>-7.64</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6138,6 +7175,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N65" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="O65" t="n">
+        <v>97.73999999999999</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6189,6 +7237,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N66" t="n">
+        <v>-76.77</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6240,6 +7299,17 @@
           <t>+13/-2</t>
         </is>
       </c>
+      <c r="N67" t="n">
+        <v>22.98</v>
+      </c>
+      <c r="O67" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6291,6 +7361,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N68" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="O68" t="n">
+        <v>97.01000000000001</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6342,6 +7423,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N69" t="n">
+        <v>-10.28</v>
+      </c>
+      <c r="O69" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6393,6 +7485,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N70" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="O70" t="n">
+        <v>100</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6444,6 +7547,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N71" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="O71" t="n">
+        <v>100</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6495,6 +7609,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N72" t="n">
+        <v>-15.52</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6546,6 +7671,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N73" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="O73" t="n">
+        <v>89.47</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6597,6 +7733,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N74" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="O74" t="n">
+        <v>97.73999999999999</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6648,6 +7795,17 @@
           <t>+13/-2</t>
         </is>
       </c>
+      <c r="N75" t="n">
+        <v>-9.380000000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6699,6 +7857,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N76" t="n">
+        <v>-17.75</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6750,6 +7919,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N77" t="n">
+        <v>-20.79</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6801,6 +7981,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N78" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6852,6 +8043,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N79" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="O79" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6903,6 +8105,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N80" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O80" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6954,6 +8167,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N81" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O81" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7005,6 +8229,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N82" t="n">
+        <v>-12.49</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7056,6 +8291,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N83" t="n">
+        <v>-8.26</v>
+      </c>
+      <c r="O83" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7107,6 +8353,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N84" t="n">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="O84" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7158,6 +8415,17 @@
           <t>+0/-15</t>
         </is>
       </c>
+      <c r="N85" t="n">
+        <v>-9.92</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7209,6 +8477,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N86" t="n">
+        <v>-21.43</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7260,6 +8539,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N87" t="n">
+        <v>-8.27</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7311,6 +8601,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N88" t="n">
+        <v>-3.91</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7362,6 +8663,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N89" t="n">
+        <v>-40.3</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7413,6 +8725,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N90" t="n">
+        <v>-12.24</v>
+      </c>
+      <c r="O90" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7464,6 +8787,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N91" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7515,6 +8849,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N92" t="n">
+        <v>-11.58</v>
+      </c>
+      <c r="O92" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7566,6 +8911,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N93" t="n">
+        <v>-14.48</v>
+      </c>
+      <c r="O93" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7617,6 +8973,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N94" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7668,6 +9035,17 @@
           <t>+0/-15</t>
         </is>
       </c>
+      <c r="N95" t="n">
+        <v>-18.64</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7719,6 +9097,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N96" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7770,6 +9159,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N97" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="O97" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7821,6 +9221,17 @@
           <t>+0/-15</t>
         </is>
       </c>
+      <c r="N98" t="n">
+        <v>-11.12</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7872,6 +9283,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N99" t="n">
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7923,6 +9345,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N100" t="n">
+        <v>-7.23</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7974,6 +9407,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N101" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O101" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8015,7 +9459,7 @@
         <v>15</v>
       </c>
       <c r="K102" t="n">
-        <v>4.037055400489961e-66</v>
+        <v>4.037055400489962e-66</v>
       </c>
       <c r="L102" t="n">
         <v>-0.4868778280542987</v>
@@ -8025,6 +9469,17 @@
           <t>+0/-15</t>
         </is>
       </c>
+      <c r="N102" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8076,6 +9531,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N103" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8127,6 +9593,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N104" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="O104" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8178,6 +9655,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N105" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8229,6 +9717,17 @@
           <t>+1/-14</t>
         </is>
       </c>
+      <c r="N106" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="O106" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8280,6 +9779,17 @@
           <t>+0/-15</t>
         </is>
       </c>
+      <c r="N107" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="O107" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8331,6 +9841,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N108" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="O108" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8382,6 +9903,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N109" t="n">
+        <v>-25.23</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8423,7 +9955,7 @@
         <v>15</v>
       </c>
       <c r="K110" t="n">
-        <v>7.351197390495679e-55</v>
+        <v>7.351197390495678e-55</v>
       </c>
       <c r="L110" t="n">
         <v>0.4608753315649867</v>
@@ -8433,6 +9965,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N110" t="n">
+        <v>-6.89</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8484,6 +10027,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N111" t="n">
+        <v>-5.79</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8535,6 +10089,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N112" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8586,6 +10151,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N113" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="O113" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8637,6 +10213,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N114" t="n">
+        <v>-4.62</v>
+      </c>
+      <c r="O114" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8688,6 +10275,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N115" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="O115" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8739,6 +10337,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N116" t="n">
+        <v>-9.35</v>
+      </c>
+      <c r="O116" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8790,6 +10399,17 @@
           <t>+0/-15</t>
         </is>
       </c>
+      <c r="N117" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8841,6 +10461,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N118" t="n">
+        <v>-4.08</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8892,6 +10523,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N119" t="n">
+        <v>-24.5</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8943,6 +10585,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N120" t="n">
+        <v>-20.33</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8994,6 +10647,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N121" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9045,6 +10709,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N122" t="n">
+        <v>-18.62</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9096,6 +10771,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N123" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="O123" t="n">
+        <v>100</v>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9147,6 +10833,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N124" t="n">
+        <v>-3.39</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9198,6 +10895,17 @@
           <t>+0/-15</t>
         </is>
       </c>
+      <c r="N125" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="O125" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9249,6 +10957,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N126" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9300,6 +11019,17 @@
           <t>+1/-14</t>
         </is>
       </c>
+      <c r="N127" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="O127" t="n">
+        <v>100</v>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9341,7 +11071,7 @@
         <v>15</v>
       </c>
       <c r="K128" t="n">
-        <v>1.556814462631828e-55</v>
+        <v>1.556814462631827e-55</v>
       </c>
       <c r="L128" t="n">
         <v>0.2838</v>
@@ -9351,6 +11081,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N128" t="n">
+        <v>-25.93</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9402,6 +11143,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N129" t="n">
+        <v>-3.92</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9453,6 +11205,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N130" t="n">
+        <v>-25.23</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9504,6 +11267,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N131" t="n">
+        <v>-8.27</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9555,6 +11329,17 @@
           <t>+1/-14</t>
         </is>
       </c>
+      <c r="N132" t="n">
+        <v>-6.27</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9606,6 +11391,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N133" t="n">
+        <v>-7.55</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9657,6 +11453,17 @@
           <t>+1/-14</t>
         </is>
       </c>
+      <c r="N134" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="O134" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9708,6 +11515,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N135" t="n">
+        <v>-18.22</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9759,6 +11577,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N136" t="n">
+        <v>-7.34</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9810,6 +11639,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N137" t="n">
+        <v>-8.91</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9861,6 +11701,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N138" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9912,6 +11763,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N139" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9963,6 +11825,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N140" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -10014,6 +11887,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N141" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10065,6 +11949,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N142" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="O142" t="n">
+        <v>37.59</v>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -10116,6 +12011,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N143" t="n">
+        <v>-4.64</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10167,6 +12073,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N144" t="n">
+        <v>-5.68</v>
+      </c>
+      <c r="O144" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10218,6 +12135,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N145" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10269,6 +12197,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N146" t="n">
+        <v>-8.640000000000001</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10310,7 +12249,7 @@
         <v>15</v>
       </c>
       <c r="K147" t="n">
-        <v>6.170586090138004e-54</v>
+        <v>6.170586090138003e-54</v>
       </c>
       <c r="L147" t="n">
         <v>0.5800000000000001</v>
@@ -10320,6 +12259,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N147" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O147" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10371,6 +12321,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N148" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="O148" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10422,6 +12383,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N149" t="n">
+        <v>-3.05</v>
+      </c>
+      <c r="O149" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10473,6 +12445,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N150" t="n">
+        <v>-8.710000000000001</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10524,6 +12507,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N151" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="O151" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10575,6 +12569,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N152" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10626,6 +12631,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N153" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="O153" t="n">
+        <v>86.47</v>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10677,6 +12693,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N154" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="O154" t="n">
+        <v>53.38</v>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10728,6 +12755,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N155" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10779,6 +12817,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N156" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="O156" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10830,6 +12879,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N157" t="n">
+        <v>-17.36</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10881,6 +12941,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N158" t="n">
+        <v>-12.1</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10932,6 +13003,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N159" t="n">
+        <v>-9.640000000000001</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10983,6 +13065,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N160" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11034,6 +13127,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N161" t="n">
+        <v>-11.41</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11085,6 +13189,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N162" t="n">
+        <v>-33.34</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11136,6 +13251,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N163" t="n">
+        <v>-11.76</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11187,6 +13313,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N164" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="O164" t="n">
+        <v>75.19</v>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11238,6 +13375,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N165" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="O165" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11289,6 +13437,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N166" t="n">
+        <v>-27.17</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11340,6 +13499,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N167" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="O167" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11391,6 +13561,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N168" t="n">
+        <v>-16.34</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11442,6 +13623,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N169" t="n">
+        <v>-4.73</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11493,6 +13685,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N170" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11544,6 +13747,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N171" t="n">
+        <v>-16.06</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11595,6 +13809,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N172" t="n">
+        <v>-18.85</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -11646,6 +13871,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N173" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O173" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -11697,6 +13933,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N174" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="O174" t="n">
+        <v>100</v>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -11748,6 +13995,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N175" t="n">
+        <v>-40.88</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -11799,6 +14057,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N176" t="n">
+        <v>-6.63</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -11850,6 +14119,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N177" t="n">
+        <v>-42.07</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11901,6 +14181,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N178" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="O178" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -11952,6 +14243,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N179" t="n">
+        <v>-30.75</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11993,7 +14295,7 @@
         <v>15</v>
       </c>
       <c r="K180" t="n">
-        <v>4.476733763808068e-10</v>
+        <v>4.476733763808067e-10</v>
       </c>
       <c r="L180" t="n">
         <v>0.1740064446831364</v>
@@ -12003,6 +14305,17 @@
           <t>+13/-2</t>
         </is>
       </c>
+      <c r="N180" t="n">
+        <v>-3.13</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -12054,6 +14367,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N181" t="n">
+        <v>-9.119999999999999</v>
+      </c>
+      <c r="O181" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -12105,6 +14429,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N182" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O182" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -12156,6 +14491,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N183" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="O183" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -12207,6 +14553,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N184" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="O184" t="n">
+        <v>92.66</v>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -12258,6 +14615,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N185" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="O185" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -12309,6 +14677,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N186" t="n">
+        <v>-19.11</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -12360,6 +14739,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N187" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="O187" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -12411,6 +14801,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N188" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="O188" t="n">
+        <v>94.06</v>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -12462,6 +14863,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N189" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -12513,6 +14925,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N190" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="O190" t="n">
+        <v>85.58</v>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -12564,6 +14987,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N191" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="O191" t="n">
+        <v>100</v>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -12615,6 +15049,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N192" t="n">
+        <v>-33.41</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -12666,6 +15111,17 @@
           <t>+13/-2</t>
         </is>
       </c>
+      <c r="N193" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="O193" t="n">
+        <v>97.98</v>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -12717,6 +15173,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N194" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="O194" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -12768,6 +15235,17 @@
           <t>+13/-2</t>
         </is>
       </c>
+      <c r="N195" t="n">
+        <v>-33.69</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -12819,6 +15297,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N196" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O196" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -12870,6 +15359,17 @@
           <t>+12/-3</t>
         </is>
       </c>
+      <c r="N197" t="n">
+        <v>-27.09</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -12921,6 +15421,17 @@
           <t>+12/-3</t>
         </is>
       </c>
+      <c r="N198" t="n">
+        <v>-26.52</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -12972,6 +15483,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N199" t="n">
+        <v>-39.61</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -13023,6 +15545,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N200" t="n">
+        <v>-10.98</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -13074,6 +15607,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N201" t="n">
+        <v>-52.69</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -13125,6 +15669,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N202" t="n">
+        <v>-49.37</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -13176,6 +15731,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N203" t="n">
+        <v>-15.63</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -13227,6 +15793,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N204" t="n">
+        <v>-16.68</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -13278,6 +15855,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N205" t="n">
+        <v>-128.62</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0</v>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -13329,6 +15917,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N206" t="n">
+        <v>34.74</v>
+      </c>
+      <c r="O206" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -13380,6 +15979,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N207" t="n">
+        <v>-37.65</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -13431,6 +16041,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N208" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="O208" t="n">
+        <v>100</v>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -13482,6 +16103,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N209" t="n">
+        <v>-175.56</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -13533,6 +16165,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N210" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="O210" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -13584,6 +16227,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N211" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="O211" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -13635,6 +16289,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N212" t="n">
+        <v>-180.26</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -13686,6 +16351,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N213" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="O213" t="n">
+        <v>100</v>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -13737,6 +16413,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N214" t="n">
+        <v>-231.03</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -13788,6 +16475,17 @@
           <t>+13/-2</t>
         </is>
       </c>
+      <c r="N215" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="O215" t="n">
+        <v>100</v>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13839,6 +16537,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N216" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="O216" t="n">
+        <v>100</v>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -13890,6 +16599,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N217" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="O217" t="n">
+        <v>98.52</v>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13941,6 +16661,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N218" t="n">
+        <v>-177.96</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -13992,6 +16723,17 @@
           <t>+0/-15</t>
         </is>
       </c>
+      <c r="N219" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="O219" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -14043,6 +16785,17 @@
           <t>+1/-14</t>
         </is>
       </c>
+      <c r="N220" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="O220" t="n">
+        <v>74.36</v>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -14094,6 +16847,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N221" t="n">
+        <v>-4.85</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -14145,6 +16909,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N222" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="O222" t="n">
+        <v>77.20999999999999</v>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -14196,6 +16971,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N223" t="n">
+        <v>-178.7</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -14247,6 +17033,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N224" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -14298,6 +17095,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N225" t="n">
+        <v>-4.85</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -14349,6 +17157,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N226" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="O226" t="n">
+        <v>86.81999999999999</v>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -14400,6 +17219,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N227" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="O227" t="n">
+        <v>99.06999999999999</v>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -14451,6 +17281,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N228" t="n">
+        <v>-80.17</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -14502,6 +17343,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N229" t="n">
+        <v>-11.47</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -14553,6 +17405,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N230" t="n">
+        <v>-40.23</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -14604,6 +17467,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N231" t="n">
+        <v>-11.51</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -14655,6 +17529,17 @@
           <t>+1/-14</t>
         </is>
       </c>
+      <c r="N232" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O232" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -14706,6 +17591,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N233" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="O233" t="n">
+        <v>99.17</v>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -14757,6 +17653,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N234" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="O234" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14808,6 +17715,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N235" t="n">
+        <v>-7.68</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14859,6 +17777,17 @@
           <t>+14/-1</t>
         </is>
       </c>
+      <c r="N236" t="n">
+        <v>-40.67</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -14910,6 +17839,17 @@
           <t>+15/-0</t>
         </is>
       </c>
+      <c r="N237" t="n">
+        <v>-51.57</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0</v>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -14959,6 +17899,17 @@
       <c r="M238" t="inlineStr">
         <is>
           <t>+15/-0</t>
+        </is>
+      </c>
+      <c r="N238" t="n">
+        <v>-65.68000000000001</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/manuscript/supplementary/Supplementary_tables.xlsx
+++ b/manuscript/supplementary/Supplementary_tables.xlsx
@@ -1417,7 +1417,7 @@
     <row r="1" ht="90" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supplementary Table 2. The 30 directed synergistic feature pairs with the highest mean total 2D information gain (IG) across the taxa-only, functions-only and combined analyses. base_IG_1D_mean: 1D IG of the base feature; total_IG_2D_mean: joint IG of the pair (base 1D IG + IG added by the contributing feature); ig_difference_raw / ig_difference_pct: absolute and relative gain over the base feature; pair_ig_count: number of fold-run combinations (of 140 = 14 LOCO folds x 10 MDFS runs) in which the pair was among the top 2 % of pairs. interaction_information_mean: total IG of the pair minus the two individual IGs, averaged over the fold-runs in which the pair was selected; pct_fold_runs_super_additive: share of those fold-runs in which it exceeded the chance threshold obtained by within-class shuffling of the features; super_additive: that share is at least 50 %.</t>
+          <t>Supplementary Table 2. The 30 directed synergistic feature pairs with the highest mean total 2D information gain (IG) across the taxa-only, functions-only and combined analyses. base_IG_1D_mean: 1D IG of the base feature; total_IG_2D_mean: joint IG of the pair (base 1D IG + IG added by the contributing feature); ig_difference_raw / ig_difference_pct: absolute and relative gain over the base feature; pair_ig_count: number of fold-run combinations (of 140 = 14 LOCO folds x 10 MDFS runs) in which the pair was among the top 2 % of pairs (pairs selected in fewer than 84 of the 140 fold-runs are included when their mean total IG over those fold-runs ranks among the 30 highest). interaction_information_mean: total IG of the pair minus the two individual IGs, averaged over the fold-runs in which the pair was selected; pct_fold_runs_super_additive: share of those fold-runs in which it exceeded the chance threshold obtained by within-class shuffling of the features; super_additive: that share is at least 50 %.</t>
         </is>
       </c>
     </row>
@@ -2842,93 +2842,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="90" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supplementary Table 3. Sensitivity of the LOCO results to the training-set composition: mean and sample-size-weighted AUC of the three feature configurations with the main training sets and with the three cohorts that are never held out (AtezoTRIBE, COLOBIOME, NSHII) removed from every training set. The stable pairs shared by both runs are listed in R5_reviewer_checks/sensitivity_shared_stable_pairs.tsv.</t>
+          <t>Supplementary Table 3. Sensitivity of the LOCO results to the training-set composition: mean and sample-size-weighted AUC of the three feature configurations with the main training sets and with the three cohorts that are never held out (AtezoTRIBE, COLOBIOME, NSHII) removed from every training set. Below the AUC table: the 64 stable pairs (61 combined, 2 functions, 1 taxa) that were stable in both runs.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>data_type</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Unnamed: 1</t>
+          <t>scenario</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>mean_AUC</t>
+          <t>mean_AUC (main)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>mean_AUC.1</t>
+          <t>mean_AUC (no single-class / training-only cohorts)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>weighted_AUC</t>
+          <t>weighted_AUC (main)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>weighted_AUC.1</t>
+          <t>weighted_AUC (no single-class / training-only cohorts)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>training</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>no single-class / training-only cohorts</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>no single-class / training-only cohorts</t>
-        </is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>All Features</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>data_type</t>
+          <t>combined</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>scenario</t>
-        </is>
+          <t>All Features + Synthetic</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
@@ -2939,92 +2948,68 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>All Features</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.8252856375286274</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.8273834518049046</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.8011831523800486</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.8002922439761009</t>
-        </is>
+          <t>Synthetic Only</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.796</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>functions</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>All Features + Synthetic</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.8266881583528028</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.8270892117270362</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.8008645562780721</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.7996104840481115</t>
-        </is>
+          <t>All Features</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.697</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>functions</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Synthetic Only</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0.8242273202619865</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.8262329635755581</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.7986273688150384</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0.7963266114069061</t>
-        </is>
+          <t>All Features + Synthetic</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.695</v>
       </c>
     </row>
     <row r="9">
@@ -3035,92 +3020,68 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>All Features</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0.6741858512887413</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.7141845310135065</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.6637949619796543</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.6965005094594753</t>
-        </is>
+          <t>Synthetic Only</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>functions</t>
+          <t>taxa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>All Features + Synthetic</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0.6717994692131287</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.7112923435097233</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.6562332491758607</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.6947735774259121</t>
-        </is>
+          <t>All Features</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>functions</t>
+          <t>taxa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Synthetic Only</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.6666096600299534</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.7092475025956634</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.6493179339819575</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.6929046513826977</t>
-        </is>
+          <t>All Features + Synthetic</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.805</v>
       </c>
     </row>
     <row r="12">
@@ -3131,91 +3092,806 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>All Features</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0.8465370754650323</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.8450443947054113</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.8176829952517427</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0.8150865591578168</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+          <t>Synthetic Only</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Stable pairs (&gt;= 80 % of folds, frequency above both constituents) in both the main and the sensitivity run</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>data_type</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>pair (feature1__feature2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ARGSYN-PWY:_L-arginine_biosynthesis_I_(via_L-ornithine)__Fusobacterium_nucleatum</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BIOTIN-BIOSYNTHESIS-PWY:_biotin_biosynthesis_I__Fusobacterium_nucleatum</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>COBALSYN-PWY:_superpathway_of_adenosylcobalamin_salvage_from_cobinamide_I__Fusobacterium_nucleatum</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>COMPLETE-ARO-PWY:_superpathway_of_aromatic_amino_acid_biosynthesis__Fusobacterium_nucleatum</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Campylobacter_ureolyticus__Fusobacterium_nucleatum</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DENITRIFICATION-PWY:_nitrate_reduction_I_(denitrification)__Fusobacterium_nucleatum</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dialister_pneumosintes__Fusobacterium_nucleatum</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dialister_pneumosintes__Parvimonas_micra</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dialister_pneumosintes__Peptostreptococcus_stomatis</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Eikenella_corrodens__Fusobacterium_nucleatum</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FASYN-ELONG-PWY:_fatty_acid_elongation_--_saturated__Fusobacterium_nucleatum</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__GLUTORN-PWY:_L-ornithine_biosynthesis_I</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__GLYCOGENSYNTH-PWY:_glycogen_biosynthesis_I_(from_ADP-D-Glucose)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__Gemella_morbillorum</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__HSERMETANA-PWY:_L-methionine_biosynthesis_III</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__Lachnospiraceae_bacterium</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__Morganella_morganii</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-1042:_glycolysis_IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-4984:_urea_cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-5100:_pyruvate_fermentation_to_acetate_and_lactate_II</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-5505:_L-glutamate_and_L-glutamine_biosynthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-5941:_glycogen_degradation_II</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-5989:_stearate_biosynthesis_II_(bacteria_and_plants)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-6282:_palmitoleate_biosynthesis_I_(from_(5Z)-dodec-5-enoate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-6292:_superpathway_of_L-cysteine_biosynthesis_(mammalian)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-6317:_D-galactose_degradation_I_(Leloir_pathway)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-6385:_peptidoglycan_biosynthesis_III_(mycobacteria)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-6519:_8-amino-7-oxononanoate_biosynthesis_I</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-6549:_L-glutamine_biosynthesis_III</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-6628:_superpathway_of_L-phenylalanine_biosynthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-6902:_chitin_degradation_II_(Vibrio)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-6936:_seleno-amino_acid_biosynthesis_(plants)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-6969:_TCA_cycle_V_(2-oxoglutarate_synthase)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-702:_L-methionine_biosynthesis_II</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-7222:_guanosine_deoxyribonucleotides_de_novo_biosynthesis_II</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-7238:_sucrose_biosynthesis_II</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-7328:_superpathway_of_UDP-glucose-derived_O-antigen_building_blocks_biosynthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-7356:_thiamine_diphosphate_salvage_IV_(yeast)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-7357:_thiamine_phosphate_formation_from_pyrithiamine_and_oxythiamine_(yeast)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-7456:_&amp;beta;-(1,4)-mannan_degradation</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-7664:_oleate_biosynthesis_IV_(anaerobic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-7953:_UDP-N-acetylmuramoyl-pentapeptide_biosynthesis_III_(meso-diaminopimelate_containing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY-I9:_L-cysteine_biosynthesis_VI_(from_L-methionine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY0-1477:_ethanolamine_utilization</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY0-162:_superpathway_of_pyrimidine_ribonucleotides_de_novo_biosynthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY0-845:_superpathway_of_pyridoxal_5'-phosphate_biosynthesis_and_salvage</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PWY0-862:_(5Z)-dodecenoate_biosynthesis_I</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__PYRIDOXSYN-PWY:_pyridoxal_5'-phosphate_biosynthesis_I</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__Parvimonas_micra</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__Peptostreptococcus_SGB749</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__Peptostreptococcus_anaerobius</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__Peptostreptococcus_stomatis</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__Porphyromonas_SGB1980</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Fusobacterium_nucleatum__Ruthenibacterium_lactatiformans</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Mogibacterium_diversum__Peptostreptococcus_stomatis</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Parvimonas_micra__Peptostreptococcus_stomatis</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Peptostreptococcus_anaerobius__Peptostreptococcus_stomatis</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Peptostreptococcus_stomatis__Streptococcus_infantis</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Peptostreptococcus_stomatis__Streptococcus_mitis</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Peptostreptococcus_stomatis__Streptococcus_sp_263_SSPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Peptostreptococcus_stomatis__Streptococcus_sp_A12</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>HEME-BIOSYNTHESIS-II-1:_heme_b_biosynthesis_V_(aerobic)__P163-PWY:_L-lysine_fermentation_to_acetate_and_butanoate</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ORNDEG-PWY:_superpathway_of_ornithine_degradation__P163-PWY:_L-lysine_fermentation_to_acetate_and_butanoate</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>taxa</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>All Features + Synthetic</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0.8365672288329742</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0.8308599949285996</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.8090582073448832</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0.8048752657736847</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>taxa</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Synthetic Only</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0.8394939482764165</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.8363828073662285</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.8115411675189755</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0.8082685360563073</t>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Dialister_pneumosintes__Gemella_morbillorum</t>
         </is>
       </c>
     </row>
@@ -17927,7 +18603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M238"/>
+  <dimension ref="A1:R238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17943,12 +18619,17 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="31" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="90" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supplementary Table 5. Cohort-adjusted logistic regression for the stable pairs (pooled samples of the 15 two-class CRC cohorts, log10 relative abundances, cohort as fixed effect): likelihood-ratio p-values of the additive model against the cohort-only model (p_pair_beyond_cohort) and of the model with a multiplicative interaction term against the additive model (p_interaction), with Benjamini-Hochberg q-values.</t>
+          <t>Supplementary Table 5. Cohort-adjusted logistic regression for the stable pairs (pooled samples of the 15 two-class CRC cohorts, log10 relative abundances, cohort as fixed effect): likelihood-ratio p-values of the additive model against the cohort-only model (p_pair_beyond_cohort) and of the model with a multiplicative interaction term against the additive model (p_interaction), with Benjamini-Hochberg q-values; and Spearman correlations, on the same pooled samples, between the synthetic feature (the encoding used in Figure 3) and each constituent (spearman_synthetic_vs_f1 / _f2), between the two constituents (spearman_f1_vs_f2) and the larger absolute correlation with a constituent (max_abs_corr_with_constituent).</t>
         </is>
       </c>
     </row>
@@ -18018,6 +18699,31 @@
           <t>q_pair_beyond_cohort</t>
         </is>
       </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>transformation</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>spearman_synthetic_vs_f1</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>spearman_synthetic_vs_f2</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>spearman_f1_vs_f2</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>max_abs_corr_with_constituent</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18067,6 +18773,23 @@
       <c r="M4" t="n">
         <v>2.53365310812423e-35</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.5971503456114663</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.7985887414945806</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.0481770305830505</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.7985887414945806</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18116,6 +18839,23 @@
       <c r="M5" t="n">
         <v>2.607069847191818e-35</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.7748236296383346</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.5589947909004931</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.0204042200852535</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.7748236296383346</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18165,6 +18905,23 @@
       <c r="M6" t="n">
         <v>1.331210238813435e-14</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.9568295861688776</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.8435260125059263</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.6900709676584955</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.9568295861688776</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18214,6 +18971,23 @@
       <c r="M7" t="n">
         <v>1.102551418756095e-09</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0.8835624189648684</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.4713810786584265</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.0423006297885649</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.8835624189648684</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18263,6 +19037,23 @@
       <c r="M8" t="n">
         <v>4.040087963951305e-12</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0.9560024856910144</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.8417154813176452</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.6865513222618049</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.9560024856910144</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18312,6 +19103,23 @@
       <c r="M9" t="n">
         <v>1.825836310657621e-81</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5435729622279102</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.7022262128762912</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.1461901989295945</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.7022262128762912</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18361,6 +19169,23 @@
       <c r="M10" t="n">
         <v>4.884914160948241e-91</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0.4983854511674008</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.9204764078076298</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1906664454543321</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.9204764078076298</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -18410,6 +19235,23 @@
       <c r="M11" t="n">
         <v>7.329176836662467e-101</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0.7938992203793872</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.8725364812112902</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.5093869868622667</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.8725364812112902</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -18459,6 +19301,23 @@
       <c r="M12" t="n">
         <v>6.06710362263095e-98</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0.9113538782393512</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.8415790500519053</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.6383777893366829</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.9113538782393512</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18508,6 +19367,23 @@
       <c r="M13" t="n">
         <v>2.566182310843126e-100</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0.7555028471410009</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.9030638476168478</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.5046549759694134</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.9030638476168478</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18557,6 +19433,23 @@
       <c r="M14" t="n">
         <v>5.959699412582679e-80</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0.5857683147325032</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.8349993508372038</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.1075062307719803</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.8349993508372038</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18606,6 +19499,23 @@
       <c r="M15" t="n">
         <v>9.969808929903476e-85</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0.722755372955863</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.656071759621792</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.0544186531393244</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.722755372955863</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18655,6 +19565,23 @@
       <c r="M16" t="n">
         <v>1.027411980360958e-83</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0.6644791170102962</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.7059413383000428</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.0406778095690479</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.7059413383000428</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18704,6 +19631,23 @@
       <c r="M17" t="n">
         <v>4.823832282850504e-80</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0.6872869808723584</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.5569161865236467</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1592440003733136</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.6872869808723584</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18753,6 +19697,23 @@
       <c r="M18" t="n">
         <v>1.691944761700769e-35</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0.6756322171610243</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.796118953838622</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1308556823981116</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.796118953838622</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18802,6 +19763,23 @@
       <c r="M19" t="n">
         <v>2.151276052944042e-36</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0.5018891357486436</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.828748284186286</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.01642088748183</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.828748284186286</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -18851,6 +19829,23 @@
       <c r="M20" t="n">
         <v>1.00190724370803e-34</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0.8103097365688335</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.5612096639187277</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.0024575325960628</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.8103097365688335</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -18900,6 +19895,23 @@
       <c r="M21" t="n">
         <v>7.57918175454588e-37</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.770068765200415</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.592010852744611</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.0044883237677439</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.770068765200415</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -18949,6 +19961,23 @@
       <c r="M22" t="n">
         <v>1.301232594752328e-20</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.7224783507810695</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.8180408050671604</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.2428192933221603</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.8180408050671604</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -18998,6 +20027,23 @@
       <c r="M23" t="n">
         <v>5.851355183331536e-37</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.5374792242037538</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.8108252399068933</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.0007146722173383</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.8108252399068933</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -19047,6 +20093,23 @@
       <c r="M24" t="n">
         <v>2.662634792568204e-37</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0.7695938268031611</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.6202092787787983</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.0037424920268355</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.7695938268031611</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -19096,6 +20159,23 @@
       <c r="M25" t="n">
         <v>4.223740462303403e-80</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>0.5398607886318952</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.6471668284845924</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.2225931598908087</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.6471668284845924</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -19145,6 +20225,23 @@
       <c r="M26" t="n">
         <v>1.431122122431651e-79</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>0.8291901482417547</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.7446065050395282</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.2978148656032531</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.8291901482417547</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -19194,6 +20291,23 @@
       <c r="M27" t="n">
         <v>1.385243519862478e-79</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>0.6738668747030521</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.7595763017676515</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.1386509672450294</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.7595763017676515</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -19243,6 +20357,23 @@
       <c r="M28" t="n">
         <v>1.305818661376272e-80</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>0.6761624145462214</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.8045316016333995</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.1699485161208165</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.8045316016333995</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -19292,6 +20423,23 @@
       <c r="M29" t="n">
         <v>4.427391921428602e-85</v>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>0.52388167670195</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-0.7550492013639392</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.1111480569387776</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.7550492013639392</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -19341,6 +20489,23 @@
       <c r="M30" t="n">
         <v>1.586249038745573e-83</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>0.8942788092123818</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.4995769128838963</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.1197763556697239</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.8942788092123818</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -19390,6 +20555,23 @@
       <c r="M31" t="n">
         <v>9.524577351892066e-81</v>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>0.8231532968290378</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.6781728323718874</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.2002523792745004</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.8231532968290378</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -19439,6 +20621,23 @@
       <c r="M32" t="n">
         <v>2.440759881644728e-83</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>0.5622173023922249</v>
+      </c>
+      <c r="P32" t="n">
+        <v>-0.7281585964052951</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.1064463344277723</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.7281585964052951</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -19488,6 +20687,23 @@
       <c r="M33" t="n">
         <v>3.232727937303119e-91</v>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>0.4639699021600997</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.940868777694601</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.211618523566041</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.940868777694601</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -19537,6 +20753,23 @@
       <c r="M34" t="n">
         <v>1.204894215641001e-85</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>0.423554727639566</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.9193692400041402</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.0935339296923499</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.9193692400041402</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -19586,6 +20819,23 @@
       <c r="M35" t="n">
         <v>1.139718166609805e-88</v>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>0.9224471559728182</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.5374318836680044</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.2483673578646879</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.9224471559728182</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -19635,6 +20885,23 @@
       <c r="M36" t="n">
         <v>9.249608731791261e-87</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>0.946762162131627</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.4735359198207304</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.235821323432064</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.946762162131627</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -19684,6 +20951,23 @@
       <c r="M37" t="n">
         <v>1.079419980247506e-72</v>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>0.5983500218610834</v>
+      </c>
+      <c r="P37" t="n">
+        <v>-0.8138937399630417</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>-0.1174952545719674</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.8138937399630417</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -19733,6 +21017,23 @@
       <c r="M38" t="n">
         <v>1.72919572346016e-83</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>0.894280606919846</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.4996060365655714</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.1197763556697239</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.894280606919846</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -19782,6 +21083,23 @@
       <c r="M39" t="n">
         <v>1.455728048809503e-92</v>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>0.5840171790608271</v>
+      </c>
+      <c r="P39" t="n">
+        <v>-0.8523610707833852</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>-0.1142320114537998</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.8523610707833852</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -19831,6 +21149,23 @@
       <c r="M40" t="n">
         <v>3.321552984495183e-37</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>0.602841929470293</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.7849636954312214</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.008197759280389599</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.7849636954312214</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -19880,6 +21215,23 @@
       <c r="M41" t="n">
         <v>6.181440234139726e-36</v>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>0.5650521601627543</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.8016742593496706</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.0020933324844809</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.8016742593496706</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -19929,6 +21281,23 @@
       <c r="M42" t="n">
         <v>1.885482477654387e-17</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>0.6453517461228208</v>
+      </c>
+      <c r="P42" t="n">
+        <v>-0.039071817993335</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.6432756495973404</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.6453517461228208</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -19978,6 +21347,23 @@
       <c r="M43" t="n">
         <v>1.615158539453167e-80</v>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>0.6202415596396584</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.7930077333836911</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.1162121042474824</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.7930077333836911</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -20027,6 +21413,23 @@
       <c r="M44" t="n">
         <v>2.791058646279437e-80</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>0.5643082643363777</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.8454059989739325</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.09526429139549911</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.8454059989739325</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -20076,6 +21479,23 @@
       <c r="M45" t="n">
         <v>5.285259702914835e-81</v>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>0.4741410192260504</v>
+      </c>
+      <c r="P45" t="n">
+        <v>-0.7243143651164746</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.2039683553161117</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.7243143651164746</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -20125,6 +21545,23 @@
       <c r="M46" t="n">
         <v>1.398282350086292e-69</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>0.583563307146483</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.7978282306551536</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.059332028704878</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.7978282306551536</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -20174,6 +21611,23 @@
       <c r="M47" t="n">
         <v>1.170125485853081e-83</v>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>0.7157950620010866</v>
+      </c>
+      <c r="P47" t="n">
+        <v>-0.6614272069548874</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>-0.0489102353029433</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.7157950620010866</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -20223,6 +21677,23 @@
       <c r="M48" t="n">
         <v>1.970470666722437e-93</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>0.8591299461890313</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.8743595530449751</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.5868816574008744</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.8743595530449751</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -20272,6 +21743,23 @@
       <c r="M49" t="n">
         <v>5.495821922706693e-80</v>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>0.3152941583278781</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.9512663409437182</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.0376606624025434</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.9512663409437182</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -20321,6 +21809,23 @@
       <c r="M50" t="n">
         <v>5.325524791495509e-80</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>0.584437409596916</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.8424190051832563</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.1113349504054969</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.8424190051832563</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -20370,6 +21875,23 @@
       <c r="M51" t="n">
         <v>1.358518716267307e-79</v>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>0.6398404546158285</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.7711965296185236</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.059460773638801</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.7711965296185236</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -20419,6 +21941,23 @@
       <c r="M52" t="n">
         <v>9.736275078716469e-30</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>0.7402930186913851</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.5986049128714385</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>-0.0220652589176276</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.7402930186913851</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -20468,6 +22007,23 @@
       <c r="M53" t="n">
         <v>2.104272477656381e-21</v>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>0.6472551194781994</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.7090943306283641</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>-0.0057733479607618</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.7090943306283641</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -20517,6 +22073,23 @@
       <c r="M54" t="n">
         <v>2.163483288083539e-09</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>0.962145399945036</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.7799948333319913</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.6120890603596271</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.962145399945036</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -20566,6 +22139,23 @@
       <c r="M55" t="n">
         <v>1.171796302839304e-80</v>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>0.8267330620503848</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.5315606179528717</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.0456626263180406</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.8267330620503848</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -20615,6 +22205,23 @@
       <c r="M56" t="n">
         <v>1.562329872161143e-79</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>0.8388646952210548</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.4595980174500215</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>-0.0547379875490677</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.8388646952210548</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -20664,6 +22271,23 @@
       <c r="M57" t="n">
         <v>1.092790064217599e-81</v>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>0.5030311448178558</v>
+      </c>
+      <c r="P57" t="n">
+        <v>-0.9108259135174228</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>-0.1396586533375566</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.9108259135174228</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -20713,6 +22337,23 @@
       <c r="M58" t="n">
         <v>8.273674165524963e-93</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>0.536984217731908</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-0.8912566781009646</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>-0.1353289676334761</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.8912566781009646</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -20762,6 +22403,23 @@
       <c r="M59" t="n">
         <v>1.174281614165014e-84</v>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>0.8409367512742277</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.6356782954020229</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.179397561041329</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.8409367512742277</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -20811,6 +22469,23 @@
       <c r="M60" t="n">
         <v>9.266540577373647e-81</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>0.7230106635588839</v>
+      </c>
+      <c r="P60" t="n">
+        <v>-0.5246231880922181</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.152042877397258</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.7230106635588839</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -20860,6 +22535,23 @@
       <c r="M61" t="n">
         <v>4.019652911379074e-99</v>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>0.7399431245795146</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.8666604111747627</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.411667066270857</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.8666604111747627</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -20909,6 +22601,23 @@
       <c r="M62" t="n">
         <v>2.930856516020008e-81</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>0.5443764831599021</v>
+      </c>
+      <c r="P62" t="n">
+        <v>-0.6571622381711948</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0.2010801398468688</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.6571622381711948</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -20958,6 +22667,23 @@
       <c r="M63" t="n">
         <v>9.340380708933904e-80</v>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>0.5634348797532265</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-0.8034929241288234</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>-0.0363500620005213</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.8034929241288234</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -21007,6 +22733,23 @@
       <c r="M64" t="n">
         <v>3.533987595634544e-80</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>0.6858974684978445</v>
+      </c>
+      <c r="P64" t="n">
+        <v>-0.4934838660384074</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0.2029579691409906</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0.6858974684978445</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -21056,6 +22799,23 @@
       <c r="M65" t="n">
         <v>1.501755387378183e-80</v>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>0.605465369937274</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.8367359985638259</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0.1333053666050186</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0.8367359985638259</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -21105,6 +22865,23 @@
       <c r="M66" t="n">
         <v>5.435522704790432e-91</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>0.4984305683467909</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.9204656710969222</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.1906664454543321</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.9204656710969222</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -21154,6 +22931,23 @@
       <c r="M67" t="n">
         <v>1.968191126581041e-86</v>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>0.5895720504517765</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.8793517155083993</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.1998488331620522</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.8793517155083993</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -21203,6 +22997,23 @@
       <c r="M68" t="n">
         <v>5.204519599121564e-93</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>0.8958947384382818</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.8414953750090997</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.6073592931473923</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.8958947384382818</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -21252,6 +23063,23 @@
       <c r="M69" t="n">
         <v>1.550492922598569e-82</v>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>0.765533538325643</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.9096611246337338</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0.4915925435656691</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.9096611246337338</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -21301,6 +23129,23 @@
       <c r="M70" t="n">
         <v>6.561785604521875e-11</v>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>0.9180028488644828</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.450549449864274</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0.163958006500885</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.9180028488644828</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -21350,6 +23195,23 @@
       <c r="M71" t="n">
         <v>3.998446970849209e-80</v>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>0.5633930748279276</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.8554224699719931</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0.1211769595031558</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0.8554224699719931</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -21399,6 +23261,23 @@
       <c r="M72" t="n">
         <v>2.844342865220882e-80</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>0.6385637113415723</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.7770983356425286</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0.1097490497627529</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0.7770983356425286</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -21448,6 +23327,23 @@
       <c r="M73" t="n">
         <v>1.5068986194832e-81</v>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>0.6507438114492198</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.8210411370727925</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0.1587384835893514</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0.8210411370727925</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -21497,6 +23393,23 @@
       <c r="M74" t="n">
         <v>5.233849237845172e-117</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
+        <v>0.8922892329578354</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.7834231503122322</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0.5042897696403327</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.8922892329578354</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -21546,6 +23459,23 @@
       <c r="M75" t="n">
         <v>2.16953953962919e-93</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>0.3545399692244949</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.9910562295664188</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0.266466361479618</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0.9910562295664188</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -21595,6 +23525,23 @@
       <c r="M76" t="n">
         <v>1.993999657447101e-93</v>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
+        <v>0.9075817028184314</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.4911746717986339</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0.1455792022993061</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.9075817028184314</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -21644,6 +23591,23 @@
       <c r="M77" t="n">
         <v>1.749174337286787e-95</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O77" t="n">
+        <v>0.932219621623574</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.4160200870963513</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0.1204318815642425</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0.932219621623574</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -21693,6 +23657,23 @@
       <c r="M78" t="n">
         <v>1.102260711813846e-97</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O78" t="n">
+        <v>0.9516960318713232</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.4545405929945788</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0.2199072516318244</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.9516960318713232</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -21742,6 +23723,23 @@
       <c r="M79" t="n">
         <v>9.553367615093193e-96</v>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O79" t="n">
+        <v>0.7866926932127726</v>
+      </c>
+      <c r="P79" t="n">
+        <v>-0.6182663920538845</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>-0.1076025524501364</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0.7866926932127726</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -21791,6 +23789,23 @@
       <c r="M80" t="n">
         <v>2.594691525718154e-96</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O80" t="n">
+        <v>0.7614797568091847</v>
+      </c>
+      <c r="P80" t="n">
+        <v>-0.6560545805306758</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>-0.1059958097001733</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.7614797568091847</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -21840,6 +23855,23 @@
       <c r="M81" t="n">
         <v>3.005821749219094e-92</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O81" t="n">
+        <v>0.9450850361017044</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.3642819118358792</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0.0690438131414864</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0.9450850361017044</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -21889,6 +23921,23 @@
       <c r="M82" t="n">
         <v>1.244454135005723e-94</v>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O82" t="n">
+        <v>0.788139619513501</v>
+      </c>
+      <c r="P82" t="n">
+        <v>-0.4395897015635684</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0.1218248418767805</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0.788139619513501</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -21938,6 +23987,23 @@
       <c r="M83" t="n">
         <v>1.76050687704159e-100</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O83" t="n">
+        <v>0.9271031383522316</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0.5057199431524062</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0.2114374933366637</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0.9271031383522316</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -21987,6 +24053,23 @@
       <c r="M84" t="n">
         <v>1.147183022376028e-106</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O84" t="n">
+        <v>0.8723806962200241</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0.8148930073620887</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0.5091152138781886</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0.8723806962200241</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -22036,6 +24119,23 @@
       <c r="M85" t="n">
         <v>6.313840808485624e-112</v>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O85" t="n">
+        <v>0.8708236008101715</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0.8306016189861966</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0.5383374693526622</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0.8708236008101715</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -22085,6 +24185,23 @@
       <c r="M86" t="n">
         <v>1.453102520246996e-107</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O86" t="n">
+        <v>0.7458327230257141</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.9287110381750012</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0.535419148425475</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0.9287110381750012</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -22134,6 +24251,23 @@
       <c r="M87" t="n">
         <v>6.529092564685256e-94</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O87" t="n">
+        <v>0.7733416152951433</v>
+      </c>
+      <c r="P87" t="n">
+        <v>-0.6336500053037769</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>-0.1008751967655349</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0.7733416152951433</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -22183,6 +24317,23 @@
       <c r="M88" t="n">
         <v>3.707129419783273e-93</v>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O88" t="n">
+        <v>0.7843712460294838</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0.5257124052188152</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>-0.0367486355727032</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0.7843712460294838</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -22232,6 +24383,23 @@
       <c r="M89" t="n">
         <v>4.263668586303692e-92</v>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O89" t="n">
+        <v>0.3674458305672049</v>
+      </c>
+      <c r="P89" t="n">
+        <v>-0.7632498523108558</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0.2419922864282597</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0.7632498523108558</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -22281,6 +24449,23 @@
       <c r="M90" t="n">
         <v>2.737808003433425e-99</v>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O90" t="n">
+        <v>0.7884428870973875</v>
+      </c>
+      <c r="P90" t="n">
+        <v>-0.6385999177381894</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>-0.1387204905097845</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0.7884428870973875</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -22330,6 +24515,23 @@
       <c r="M91" t="n">
         <v>1.443281528404934e-97</v>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O91" t="n">
+        <v>0.4692944563005435</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.9624078644764864</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0.2866077081488942</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0.9624078644764864</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -22379,6 +24581,23 @@
       <c r="M92" t="n">
         <v>9.5200501558255e-92</v>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O92" t="n">
+        <v>0.7869986756864413</v>
+      </c>
+      <c r="P92" t="n">
+        <v>-0.638705832230991</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>-0.148674674618618</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0.7869986756864413</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -22428,6 +24647,23 @@
       <c r="M93" t="n">
         <v>1.033530307055284e-91</v>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O93" t="n">
+        <v>0.7885720528210759</v>
+      </c>
+      <c r="P93" t="n">
+        <v>-0.6389874472064891</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>-0.1510452515872861</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0.7885720528210759</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -22477,6 +24713,23 @@
       <c r="M94" t="n">
         <v>1.464201305846845e-95</v>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O94" t="n">
+        <v>0.7688775810982913</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0.7397355881410166</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0.2319491878836418</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0.7688775810982913</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -22526,6 +24779,23 @@
       <c r="M95" t="n">
         <v>5.14313978598395e-92</v>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O95" t="n">
+        <v>0.7885984567682679</v>
+      </c>
+      <c r="P95" t="n">
+        <v>-0.6355944216859692</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>-0.1469245303519027</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0.7885984567682679</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -22575,6 +24845,23 @@
       <c r="M96" t="n">
         <v>3.357083588594581e-92</v>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O96" t="n">
+        <v>0.7884707382745983</v>
+      </c>
+      <c r="P96" t="n">
+        <v>-0.6318770631890761</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>-0.1359970369662826</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0.7884707382745983</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -22624,6 +24911,23 @@
       <c r="M97" t="n">
         <v>2.220219195884721e-97</v>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O97" t="n">
+        <v>0.7882343624089243</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.6376623101627925</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0.1264355855958535</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0.7882343624089243</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -22673,6 +24977,23 @@
       <c r="M98" t="n">
         <v>1.051768395064962e-97</v>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O98" t="n">
+        <v>0.7886658725295369</v>
+      </c>
+      <c r="P98" t="n">
+        <v>-0.722154170820375</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>-0.2652462501812313</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0.7886658725295369</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -22722,6 +25043,23 @@
       <c r="M99" t="n">
         <v>2.054314176412994e-98</v>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O99" t="n">
+        <v>0.7884559441701889</v>
+      </c>
+      <c r="P99" t="n">
+        <v>-0.6758069321206442</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>-0.1909739028913609</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0.7884559441701889</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -22771,6 +25109,23 @@
       <c r="M100" t="n">
         <v>4.215612743905403e-98</v>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O100" t="n">
+        <v>0.7856133933405417</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.5891752501163251</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0.0487653778987151</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0.7856133933405417</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -22820,6 +25175,23 @@
       <c r="M101" t="n">
         <v>1.069061879964512e-91</v>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O101" t="n">
+        <v>0.7884968942014122</v>
+      </c>
+      <c r="P101" t="n">
+        <v>-0.6522025077258793</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>-0.1685505285310923</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0.7884968942014122</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -22869,6 +25241,23 @@
       <c r="M102" t="n">
         <v>1.179939281138483e-97</v>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O102" t="n">
+        <v>0.7883368108263413</v>
+      </c>
+      <c r="P102" t="n">
+        <v>-0.5702884808261449</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>-0.0431041419880737</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0.7883368108263413</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -22918,6 +25307,23 @@
       <c r="M103" t="n">
         <v>4.263254508285318e-98</v>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O103" t="n">
+        <v>0.7822289093872498</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0.6656331124298848</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0.1510040529479854</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.7822289093872498</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -22967,6 +25373,23 @@
       <c r="M104" t="n">
         <v>1.305812433965123e-94</v>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O104" t="n">
+        <v>0.7874325331074954</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0.6652933067882968</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0.1552069623466623</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.7874325331074954</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -23016,6 +25439,23 @@
       <c r="M105" t="n">
         <v>3.667839756200103e-97</v>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O105" t="n">
+        <v>0.7886095870160901</v>
+      </c>
+      <c r="P105" t="n">
+        <v>-0.6494134526640991</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>-0.1587302216702293</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0.7886095870160901</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -23065,6 +25505,23 @@
       <c r="M106" t="n">
         <v>3.295711412961264e-93</v>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O106" t="n">
+        <v>0.7882694270677018</v>
+      </c>
+      <c r="P106" t="n">
+        <v>-0.6123172654647462</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>-0.09170334390839779</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0.7882694270677018</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -23114,6 +25571,23 @@
       <c r="M107" t="n">
         <v>4.512715827684095e-91</v>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O107" t="n">
+        <v>0.7719154865768545</v>
+      </c>
+      <c r="P107" t="n">
+        <v>-0.6192289803470212</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>-0.078748260305619</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0.7719154865768545</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -23163,6 +25637,23 @@
       <c r="M108" t="n">
         <v>2.570425059389941e-93</v>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O108" t="n">
+        <v>0.7809561726232385</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0.7295139199961255</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0.2451365813815352</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0.7809561726232385</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -23212,6 +25703,23 @@
       <c r="M109" t="n">
         <v>3.255094910114785e-94</v>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O109" t="n">
+        <v>0.7874605494602531</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0.667795539325154</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0.1582993680309623</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0.7874605494602531</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -23261,6 +25769,23 @@
       <c r="M110" t="n">
         <v>1.802619632759717e-92</v>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O110" t="n">
+        <v>0.7886412038360289</v>
+      </c>
+      <c r="P110" t="n">
+        <v>-0.6627203681664507</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>-0.1777425055445883</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0.7886412038360289</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -23310,6 +25835,23 @@
       <c r="M111" t="n">
         <v>1.443281528404934e-97</v>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O111" t="n">
+        <v>0.7882748506244258</v>
+      </c>
+      <c r="P111" t="n">
+        <v>-0.5817941360858154</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>-0.0592403219990225</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0.7882748506244258</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -23359,6 +25901,23 @@
       <c r="M112" t="n">
         <v>2.294515188391187e-92</v>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O112" t="n">
+        <v>0.7719052850027565</v>
+      </c>
+      <c r="P112" t="n">
+        <v>-0.5272403951139816</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0.0394876052901136</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0.7719052850027565</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -23408,6 +25967,23 @@
       <c r="M113" t="n">
         <v>1.120550841903306e-98</v>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O113" t="n">
+        <v>0.7883656407506352</v>
+      </c>
+      <c r="P113" t="n">
+        <v>-0.6690414583123104</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>-0.1735076607103036</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0.7883656407506352</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -23457,6 +26033,23 @@
       <c r="M114" t="n">
         <v>3.787928236531711e-94</v>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O114" t="n">
+        <v>0.7875177821682529</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0.6661190856368471</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0.1568789094053362</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0.7875177821682529</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -23506,6 +26099,23 @@
       <c r="M115" t="n">
         <v>4.514466235063219e-87</v>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O115" t="n">
+        <v>0.8982124312814662</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0.5262612953408502</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0.1732107281095526</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0.8982124312814662</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -23555,6 +26165,23 @@
       <c r="M116" t="n">
         <v>1.356916294566688e-91</v>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O116" t="n">
+        <v>0.5019456783739694</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0.9313690374426</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0.2368304568912123</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0.9313690374426</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -23604,6 +26231,23 @@
       <c r="M117" t="n">
         <v>2.575343572012214e-82</v>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O117" t="n">
+        <v>0.7737367858729446</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.6496894816427909</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.067019377958574</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.7737367858729446</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -23653,6 +26297,23 @@
       <c r="M118" t="n">
         <v>1.43417145365986e-72</v>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O118" t="n">
+        <v>0.8102386839193191</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.572557580174245</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.0285243902835221</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.8102386839193191</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -23702,6 +26363,23 @@
       <c r="M119" t="n">
         <v>9.846464368488566e-82</v>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O119" t="n">
+        <v>0.5306643249299902</v>
+      </c>
+      <c r="P119" t="n">
+        <v>-0.630940565247241</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.2499249843545387</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.630940565247241</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -23751,6 +26429,23 @@
       <c r="M120" t="n">
         <v>8.545493535271203e-101</v>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O120" t="n">
+        <v>0.7555188473393336</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.903065254411747</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.5046550358437855</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.903065254411747</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -23800,6 +26495,23 @@
       <c r="M121" t="n">
         <v>1.333953470627104e-92</v>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O121" t="n">
+        <v>0.7444442106245298</v>
+      </c>
+      <c r="P121" t="n">
+        <v>-0.6729698374514582</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>-0.1112209323302269</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.7444442106245298</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -23849,6 +26561,23 @@
       <c r="M122" t="n">
         <v>4.598458516624117e-74</v>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O122" t="n">
+        <v>0.5994782573880015</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.8557339299334692</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.1602203344364561</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.8557339299334692</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -23898,6 +26627,23 @@
       <c r="M123" t="n">
         <v>1.646261026553586e-79</v>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O123" t="n">
+        <v>0.8292645164649023</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.7445629716869561</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.2978116806294073</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.8292645164649023</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -23947,6 +26693,23 @@
       <c r="M124" t="n">
         <v>4.215612743905403e-98</v>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O124" t="n">
+        <v>0.9113522858594972</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.8416252781018916</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.6383777893366829</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.9113522858594972</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -23996,6 +26759,23 @@
       <c r="M125" t="n">
         <v>3.454855415852401e-08</v>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O125" t="n">
+        <v>0.9549994273493486</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.4454543037594162</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.1994838638548149</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.9549994273493486</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -24045,6 +26825,23 @@
       <c r="M126" t="n">
         <v>6.716954699225586e-75</v>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O126" t="n">
+        <v>0.5516448664924575</v>
+      </c>
+      <c r="P126" t="n">
+        <v>-0.7943223092487401</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>-0.0175075532775271</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.7943223092487401</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -24094,6 +26891,23 @@
       <c r="M127" t="n">
         <v>4.233012888913128e-85</v>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O127" t="n">
+        <v>0.5994483489129147</v>
+      </c>
+      <c r="P127" t="n">
+        <v>-0.7411306630254747</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.0097398257588081</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.7411306630254747</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -24143,6 +26957,23 @@
       <c r="M128" t="n">
         <v>1.987424185211462e-86</v>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O128" t="n">
+        <v>0.6399506465788418</v>
+      </c>
+      <c r="P128" t="n">
+        <v>-0.6569010510416512</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.0725194995735072</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.6569010510416512</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -24192,6 +27023,23 @@
       <c r="M129" t="n">
         <v>1.970470666722437e-93</v>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O129" t="n">
+        <v>0.7810340279147849</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.6268163402357328</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.1006946760621222</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.7810340279147849</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -24241,6 +27089,23 @@
       <c r="M130" t="n">
         <v>2.859419793543428e-91</v>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O130" t="n">
+        <v>0.7886389374275928</v>
+      </c>
+      <c r="P130" t="n">
+        <v>-0.6380375827637952</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>-0.1422283262778608</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.7886389374275928</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -24290,6 +27155,23 @@
       <c r="M131" t="n">
         <v>8.531589068152024e-92</v>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O131" t="n">
+        <v>0.7883188933541972</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.6408390601746048</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.1308050939388718</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.7883188933541972</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -24339,6 +27221,23 @@
       <c r="M132" t="n">
         <v>3.191235370531978e-91</v>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O132" t="n">
+        <v>0.7878009965802866</v>
+      </c>
+      <c r="P132" t="n">
+        <v>-0.6155002063164535</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>-0.1130427976554945</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.7878009965802866</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -24388,6 +27287,23 @@
       <c r="M133" t="n">
         <v>5.194534185185589e-92</v>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O133" t="n">
+        <v>0.7885090907590674</v>
+      </c>
+      <c r="P133" t="n">
+        <v>-0.6659514270390117</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>-0.1795783861628887</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.7885090907590674</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -24437,6 +27353,23 @@
       <c r="M134" t="n">
         <v>2.709535209895886e-95</v>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O134" t="n">
+        <v>0.6767190807522301</v>
+      </c>
+      <c r="P134" t="n">
+        <v>-0.7886252736382753</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>-0.1935067069928522</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.7886252736382753</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -24486,6 +27419,23 @@
       <c r="M135" t="n">
         <v>7.676787426743388e-94</v>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O135" t="n">
+        <v>0.9203035359261532</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.5378090348114819</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.2244067658847597</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.9203035359261532</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -24535,6 +27485,23 @@
       <c r="M136" t="n">
         <v>1.596298771535456e-94</v>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O136" t="n">
+        <v>0.6596601156632443</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.7877260122824472</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.1485244862112248</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.7877260122824472</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -24584,6 +27551,23 @@
       <c r="M137" t="n">
         <v>2.376078036809303e-92</v>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O137" t="n">
+        <v>0.7885075955251042</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.6292299521868302</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>-0.1297857279630029</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.7885075955251042</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -24633,6 +27617,23 @@
       <c r="M138" t="n">
         <v>4.449584813282635e-95</v>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O138" t="n">
+        <v>0.9560159912509106</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.4183551635884875</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.1919099292743693</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.9560159912509106</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -24682,6 +27683,23 @@
       <c r="M139" t="n">
         <v>1.340533333669426e-97</v>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O139" t="n">
+        <v>0.7877518618765903</v>
+      </c>
+      <c r="P139" t="n">
+        <v>-0.6726758326287691</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>-0.1817192602846593</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.7877518618765903</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -24731,6 +27749,23 @@
       <c r="M140" t="n">
         <v>7.500294380686858e-99</v>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O140" t="n">
+        <v>0.7854124883432505</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.591678612514046</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.0520897475856849</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.7854124883432505</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -24780,6 +27815,23 @@
       <c r="M141" t="n">
         <v>3.83111367701758e-91</v>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O141" t="n">
+        <v>0.7870129873304299</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.6507901767874218</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.1306863612188146</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.7870129873304299</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -24829,6 +27881,23 @@
       <c r="M142" t="n">
         <v>5.2567543443531e-92</v>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O142" t="n">
+        <v>0.7870346741997308</v>
+      </c>
+      <c r="P142" t="n">
+        <v>-0.6403721105677764</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>-0.1362931662097774</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.7870346741997308</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -24878,6 +27947,23 @@
       <c r="M143" t="n">
         <v>2.759109177166653e-101</v>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O143" t="n">
+        <v>0.7885052335532609</v>
+      </c>
+      <c r="P143" t="n">
+        <v>-0.6618374635227074</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>-0.1658527224281812</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.7885052335532609</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -24927,6 +28013,23 @@
       <c r="M144" t="n">
         <v>1.374062841169491e-95</v>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O144" t="n">
+        <v>0.6888592588860788</v>
+      </c>
+      <c r="P144" t="n">
+        <v>-0.7886443578729502</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>-0.2112312868440201</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0.7886443578729502</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -24976,6 +28079,23 @@
       <c r="M145" t="n">
         <v>2.518802984110145e-93</v>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O145" t="n">
+        <v>0.5200971058380108</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0.7876412938321206</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>-0.0344485894880858</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0.7876412938321206</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -25025,6 +28145,23 @@
       <c r="M146" t="n">
         <v>7.892227268343734e-93</v>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O146" t="n">
+        <v>0.919254194977922</v>
+      </c>
+      <c r="P146" t="n">
+        <v>-0.3549356491702065</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>0.0053225312774194</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0.919254194977922</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -25074,6 +28211,23 @@
       <c r="M147" t="n">
         <v>4.76555844986814e-94</v>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O147" t="n">
+        <v>0.6629413150281293</v>
+      </c>
+      <c r="P147" t="n">
+        <v>-0.7886386338470944</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>-0.1748676822308358</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0.7886386338470944</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -25123,6 +28277,23 @@
       <c r="M148" t="n">
         <v>4.512715827684095e-91</v>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O148" t="n">
+        <v>0.7881185880077224</v>
+      </c>
+      <c r="P148" t="n">
+        <v>0.5902373721349715</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>0.0622589633623593</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0.7881185880077224</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -25172,6 +28343,23 @@
       <c r="M149" t="n">
         <v>2.376078036809303e-92</v>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O149" t="n">
+        <v>0.9389786543982838</v>
+      </c>
+      <c r="P149" t="n">
+        <v>0.3780871827433036</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>0.078446739126752</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0.9389786543982838</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -25221,6 +28409,23 @@
       <c r="M150" t="n">
         <v>1.187870001760545e-91</v>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O150" t="n">
+        <v>0.7885301298210223</v>
+      </c>
+      <c r="P150" t="n">
+        <v>-0.6207451042467881</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>-0.1260020521978923</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0.7885301298210223</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -25270,6 +28475,23 @@
       <c r="M151" t="n">
         <v>4.316305445388703e-93</v>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O151" t="n">
+        <v>0.6369376135985759</v>
+      </c>
+      <c r="P151" t="n">
+        <v>-0.7846730827783583</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>-0.1176613556273403</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0.7846730827783583</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -25319,6 +28541,23 @@
       <c r="M152" t="n">
         <v>5.914491870321149e-95</v>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O152" t="n">
+        <v>0.7799966705067218</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0.554454061012475</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>-0.0031357986184621</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0.7799966705067218</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -25368,6 +28607,23 @@
       <c r="M153" t="n">
         <v>4.512715827684095e-91</v>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O153" t="n">
+        <v>0.8641156073471619</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0.6740445633518534</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0.2753293210398004</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0.8641156073471619</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -25417,6 +28673,23 @@
       <c r="M154" t="n">
         <v>4.00842326559172e-93</v>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O154" t="n">
+        <v>0.7884611952682991</v>
+      </c>
+      <c r="P154" t="n">
+        <v>-0.6273819692989203</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>-0.1231020681502046</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0.7884611952682991</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -25466,6 +28739,23 @@
       <c r="M155" t="n">
         <v>2.709535209895886e-95</v>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O155" t="n">
+        <v>0.6246039103580183</v>
+      </c>
+      <c r="P155" t="n">
+        <v>-0.788678749143067</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>-0.1250020940388402</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0.788678749143067</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -25515,6 +28805,23 @@
       <c r="M156" t="n">
         <v>6.687400811914088e-92</v>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O156" t="n">
+        <v>0.6305384232567331</v>
+      </c>
+      <c r="P156" t="n">
+        <v>-0.7885139924951396</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>-0.1296519436376163</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0.7885139924951396</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -25564,6 +28871,23 @@
       <c r="M157" t="n">
         <v>1.455728048809503e-92</v>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O157" t="n">
+        <v>0.7885649091230209</v>
+      </c>
+      <c r="P157" t="n">
+        <v>-0.6402570146430185</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>-0.1538031012901955</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0.7885649091230209</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -25613,6 +28937,23 @@
       <c r="M158" t="n">
         <v>4.137378781576769e-93</v>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O158" t="n">
+        <v>0.7884875218758031</v>
+      </c>
+      <c r="P158" t="n">
+        <v>-0.6829946388799015</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>-0.2082790851726691</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0.7884875218758031</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -25662,6 +29003,23 @@
       <c r="M159" t="n">
         <v>9.052072582302122e-92</v>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O159" t="n">
+        <v>0.7850407928334757</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0.6055728474299966</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0.07445804589126449</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0.7850407928334757</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -25711,6 +29069,23 @@
       <c r="M160" t="n">
         <v>6.269547859504542e-93</v>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O160" t="n">
+        <v>0.7791616670436546</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0.614975597565652</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0.0822660239337375</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0.7791616670436546</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -25760,6 +29135,23 @@
       <c r="M161" t="n">
         <v>4.449584813282635e-95</v>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O161" t="n">
+        <v>0.7885444204703773</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0.544716877390319</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0.009720728661514501</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0.7885444204703773</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -25809,6 +29201,23 @@
       <c r="M162" t="n">
         <v>3.157076440464129e-92</v>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O162" t="n">
+        <v>0.7885596629142015</v>
+      </c>
+      <c r="P162" t="n">
+        <v>-0.631619761533419</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>-0.1416392307651956</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0.7885596629142015</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -25858,6 +29267,23 @@
       <c r="M163" t="n">
         <v>1.802619632759717e-92</v>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O163" t="n">
+        <v>0.7886412038360289</v>
+      </c>
+      <c r="P163" t="n">
+        <v>-0.6627203681664507</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>-0.1777425055445883</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0.7886412038360289</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -25907,6 +29333,23 @@
       <c r="M164" t="n">
         <v>4.316305445388703e-93</v>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O164" t="n">
+        <v>0.7832466904175859</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0.5984842451420855</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0.0692377726632144</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0.7832466904175859</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -25956,6 +29399,23 @@
       <c r="M165" t="n">
         <v>5.194534185185589e-92</v>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O165" t="n">
+        <v>0.7885019310596976</v>
+      </c>
+      <c r="P165" t="n">
+        <v>-0.6659341734648292</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>-0.179377545661333</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.7885019310596976</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -26005,6 +29465,23 @@
       <c r="M166" t="n">
         <v>4.214159200732496e-92</v>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O166" t="n">
+        <v>0.6251254470734418</v>
+      </c>
+      <c r="P166" t="n">
+        <v>-0.7885014479088895</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>-0.1251579343986277</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0.7885014479088895</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -26054,6 +29531,23 @@
       <c r="M167" t="n">
         <v>9.568845559827815e-98</v>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O167" t="n">
+        <v>0.7884154523988398</v>
+      </c>
+      <c r="P167" t="n">
+        <v>-0.6343817329853969</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>-0.1321252375162662</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0.7884154523988398</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -26103,6 +29597,23 @@
       <c r="M168" t="n">
         <v>1.051845072765407e-79</v>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O168" t="n">
+        <v>0.9054925248272534</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0.5494280974243083</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>0.2233859990348317</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0.9054925248272534</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -26152,6 +29663,23 @@
       <c r="M169" t="n">
         <v>9.56776567380434e-11</v>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O169" t="n">
+        <v>0.9777595662151444</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0.7874035883876692</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>0.6685159622019298</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0.9777595662151444</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -26201,6 +29729,23 @@
       <c r="M170" t="n">
         <v>8.962383730104407e-08</v>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O170" t="n">
+        <v>0.4501816822374006</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0.9102809109673869</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>0.1077338524038417</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0.9102809109673869</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -26250,6 +29795,23 @@
       <c r="M171" t="n">
         <v>3.533442535334607e-71</v>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O171" t="n">
+        <v>0.9144106362463116</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0.5369633235201252</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>0.2057760023364046</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0.9144106362463116</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -26299,6 +29861,23 @@
       <c r="M172" t="n">
         <v>3.25467581319314e-80</v>
       </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O172" t="n">
+        <v>0.5398183411461085</v>
+      </c>
+      <c r="P172" t="n">
+        <v>-0.6472158128632017</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>0.2225971995538883</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0.6472158128632017</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -26348,6 +29927,23 @@
       <c r="M173" t="n">
         <v>4.125801872258974e-92</v>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O173" t="n">
+        <v>0.8963790620814106</v>
+      </c>
+      <c r="P173" t="n">
+        <v>0.5678399091392334</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>0.2230810967929811</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0.8963790620814106</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -26397,6 +29993,23 @@
       <c r="M174" t="n">
         <v>2.153633238289398e-13</v>
       </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O174" t="n">
+        <v>0.683759707947491</v>
+      </c>
+      <c r="P174" t="n">
+        <v>-0.6213808348867457</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>0.0334574128033359</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0.683759707947491</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -26446,6 +30059,23 @@
       <c r="M175" t="n">
         <v>1.171027339309599e-70</v>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O175" t="n">
+        <v>0.5483348031268954</v>
+      </c>
+      <c r="P175" t="n">
+        <v>0.8502316147111311</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>0.0664670567229909</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0.8502316147111311</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -26495,6 +30125,23 @@
       <c r="M176" t="n">
         <v>1.665364994366316e-80</v>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O176" t="n">
+        <v>0.4836185429269671</v>
+      </c>
+      <c r="P176" t="n">
+        <v>-0.697653819091115</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>0.2318244327114237</v>
+      </c>
+      <c r="R176" t="n">
+        <v>0.697653819091115</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -26544,6 +30191,23 @@
       <c r="M177" t="n">
         <v>4.241504772160525e-25</v>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O177" t="n">
+        <v>0.896700217725534</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0.5323336682513354</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>0.175791537494986</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0.896700217725534</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -26593,6 +30257,23 @@
       <c r="M178" t="n">
         <v>1.696163659656843e-74</v>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O178" t="n">
+        <v>0.4400334499724881</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0.9382361969695052</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>0.1683873457664489</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0.9382361969695052</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -26642,6 +30323,23 @@
       <c r="M179" t="n">
         <v>9.420597689517864e-76</v>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O179" t="n">
+        <v>0.5174098074424008</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0.9242765423145678</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>0.23059492114257</v>
+      </c>
+      <c r="R179" t="n">
+        <v>0.9242765423145678</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -26691,6 +30389,23 @@
       <c r="M180" t="n">
         <v>4.350714597424634e-83</v>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O180" t="n">
+        <v>0.4612673429804538</v>
+      </c>
+      <c r="P180" t="n">
+        <v>0.9639665674554432</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>0.280163080937021</v>
+      </c>
+      <c r="R180" t="n">
+        <v>0.9639665674554432</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -26740,6 +30455,23 @@
       <c r="M181" t="n">
         <v>1.036303982739656e-86</v>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O181" t="n">
+        <v>0.4857509722975117</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0.9421627624034392</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>0.2411406881002712</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0.9421627624034392</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -26789,6 +30521,23 @@
       <c r="M182" t="n">
         <v>6.742205035961426e-100</v>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O182" t="n">
+        <v>0.7884708840126842</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0.6236164937721628</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>0.1087394634166156</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0.7884708840126842</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -26838,6 +30587,23 @@
       <c r="M183" t="n">
         <v>9.287318574150268e-96</v>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O183" t="n">
+        <v>0.6669228132224346</v>
+      </c>
+      <c r="P183" t="n">
+        <v>-0.7884431488966752</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>-0.1753598582247964</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0.7884431488966752</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -26887,6 +30653,23 @@
       <c r="M184" t="n">
         <v>6.835334297808391e-95</v>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O184" t="n">
+        <v>0.7876095849032558</v>
+      </c>
+      <c r="P184" t="n">
+        <v>0.6608409905045437</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>0.1489953400453802</v>
+      </c>
+      <c r="R184" t="n">
+        <v>0.7876095849032558</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -26936,6 +30719,23 @@
       <c r="M185" t="n">
         <v>3.339053449673928e-91</v>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O185" t="n">
+        <v>0.4907745820406848</v>
+      </c>
+      <c r="P185" t="n">
+        <v>-0.7878480515575517</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>0.0515805215396338</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0.7878480515575517</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -26985,6 +30785,23 @@
       <c r="M186" t="n">
         <v>1.205050143379865e-92</v>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O186" t="n">
+        <v>0.7886152621490397</v>
+      </c>
+      <c r="P186" t="n">
+        <v>-0.6802854336623534</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>-0.2077958205775578</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0.7886152621490397</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -27034,6 +30851,23 @@
       <c r="M187" t="n">
         <v>3.230110585239371e-91</v>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O187" t="n">
+        <v>0.7885395723746238</v>
+      </c>
+      <c r="P187" t="n">
+        <v>-0.6373390065388901</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>-0.1483144632189145</v>
+      </c>
+      <c r="R187" t="n">
+        <v>0.7885395723746238</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -27083,6 +30917,23 @@
       <c r="M188" t="n">
         <v>4.43000424131708e-94</v>
       </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O188" t="n">
+        <v>0.6657771196733161</v>
+      </c>
+      <c r="P188" t="n">
+        <v>0.7876059765342899</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>0.156746600299281</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0.7876059765342899</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -27132,6 +30983,23 @@
       <c r="M189" t="n">
         <v>4.512715827684095e-91</v>
       </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O189" t="n">
+        <v>0.788488201625418</v>
+      </c>
+      <c r="P189" t="n">
+        <v>0.5257355148067892</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>-0.0183489991582292</v>
+      </c>
+      <c r="R189" t="n">
+        <v>0.788488201625418</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -27181,6 +31049,23 @@
       <c r="M190" t="n">
         <v>1.294924280323565e-95</v>
       </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O190" t="n">
+        <v>0.7874386152505787</v>
+      </c>
+      <c r="P190" t="n">
+        <v>-0.6041818785873356</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>-0.08815107739412111</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0.7874386152505787</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -27230,6 +31115,23 @@
       <c r="M191" t="n">
         <v>3.665519251435372e-96</v>
       </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O191" t="n">
+        <v>0.7883759309294353</v>
+      </c>
+      <c r="P191" t="n">
+        <v>0.5254476665115195</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>-0.0193818586839899</v>
+      </c>
+      <c r="R191" t="n">
+        <v>0.7883759309294353</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -27279,6 +31181,23 @@
       <c r="M192" t="n">
         <v>1.928978269169472e-94</v>
       </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O192" t="n">
+        <v>0.7884664503667376</v>
+      </c>
+      <c r="P192" t="n">
+        <v>0.6143484660805446</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>0.1018599552897664</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0.7884664503667376</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -27328,6 +31247,23 @@
       <c r="M193" t="n">
         <v>9.444962053718633e-92</v>
       </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O193" t="n">
+        <v>0.788461035699633</v>
+      </c>
+      <c r="P193" t="n">
+        <v>-0.5716222909357224</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>-0.0530260340843214</v>
+      </c>
+      <c r="R193" t="n">
+        <v>0.788461035699633</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -27377,6 +31313,23 @@
       <c r="M194" t="n">
         <v>1.23890098428494e-92</v>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O194" t="n">
+        <v>0.7877630436281911</v>
+      </c>
+      <c r="P194" t="n">
+        <v>0.5973520623980322</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>0.07502027231260849</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0.7877630436281911</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -27426,6 +31379,23 @@
       <c r="M195" t="n">
         <v>1.560695171055817e-91</v>
       </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O195" t="n">
+        <v>0.7848407182777319</v>
+      </c>
+      <c r="P195" t="n">
+        <v>0.6472194971316315</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>0.1331132297529575</v>
+      </c>
+      <c r="R195" t="n">
+        <v>0.7848407182777319</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -27475,6 +31445,23 @@
       <c r="M196" t="n">
         <v>8.503119195717476e-93</v>
       </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O196" t="n">
+        <v>0.7849748758230817</v>
+      </c>
+      <c r="P196" t="n">
+        <v>0.5690124631900305</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>0.0251411541348294</v>
+      </c>
+      <c r="R196" t="n">
+        <v>0.7849748758230817</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -27524,6 +31511,23 @@
       <c r="M197" t="n">
         <v>5.194534185185589e-92</v>
       </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O197" t="n">
+        <v>0.7884987130175175</v>
+      </c>
+      <c r="P197" t="n">
+        <v>-0.6659463104279896</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>-0.1793634236121414</v>
+      </c>
+      <c r="R197" t="n">
+        <v>0.7884987130175175</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -27573,6 +31577,23 @@
       <c r="M198" t="n">
         <v>2.709535209895886e-95</v>
       </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O198" t="n">
+        <v>0.7861140811809745</v>
+      </c>
+      <c r="P198" t="n">
+        <v>0.5732563454520824</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>0.0309789493146892</v>
+      </c>
+      <c r="R198" t="n">
+        <v>0.7861140811809745</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -27622,6 +31643,23 @@
       <c r="M199" t="n">
         <v>3.904843932125504e-91</v>
       </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O199" t="n">
+        <v>0.5924401388186847</v>
+      </c>
+      <c r="P199" t="n">
+        <v>0.7784342695423081</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>0.0495652854226974</v>
+      </c>
+      <c r="R199" t="n">
+        <v>0.7784342695423081</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -27671,6 +31709,23 @@
       <c r="M200" t="n">
         <v>1.458120317707115e-91</v>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O200" t="n">
+        <v>0.7885403657731447</v>
+      </c>
+      <c r="P200" t="n">
+        <v>-0.5992176088202683</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>-0.09591008776716969</v>
+      </c>
+      <c r="R200" t="n">
+        <v>0.7885403657731447</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -27720,6 +31775,23 @@
       <c r="M201" t="n">
         <v>3.321374254253625e-91</v>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O201" t="n">
+        <v>0.787686641406803</v>
+      </c>
+      <c r="P201" t="n">
+        <v>-0.5997527164401349</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>-0.090635285042911</v>
+      </c>
+      <c r="R201" t="n">
+        <v>0.787686641406803</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -27769,6 +31841,23 @@
       <c r="M202" t="n">
         <v>4.00842326559172e-93</v>
       </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O202" t="n">
+        <v>0.7868607848014033</v>
+      </c>
+      <c r="P202" t="n">
+        <v>-0.5044476368359887</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>0.0434084714674211</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0.7868607848014033</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -27818,6 +31907,23 @@
       <c r="M203" t="n">
         <v>3.321374254253625e-91</v>
       </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O203" t="n">
+        <v>0.447304550381337</v>
+      </c>
+      <c r="P203" t="n">
+        <v>0.7886031571544633</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>-0.0984476527042676</v>
+      </c>
+      <c r="R203" t="n">
+        <v>0.7886031571544633</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -27867,6 +31973,23 @@
       <c r="M204" t="n">
         <v>3.005821749219094e-92</v>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O204" t="n">
+        <v>0.5087629597622091</v>
+      </c>
+      <c r="P204" t="n">
+        <v>-0.7292527144981564</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>0.1649301046181283</v>
+      </c>
+      <c r="R204" t="n">
+        <v>0.7292527144981564</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -27916,6 +32039,23 @@
       <c r="M205" t="n">
         <v>9.148708166562248e-92</v>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O205" t="n">
+        <v>0.7879488221071484</v>
+      </c>
+      <c r="P205" t="n">
+        <v>0.5342803184923565</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>-0.0091483805746864</v>
+      </c>
+      <c r="R205" t="n">
+        <v>0.7879488221071484</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -27965,6 +32105,23 @@
       <c r="M206" t="n">
         <v>2.296275936422399e-91</v>
       </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O206" t="n">
+        <v>0.9563749362175612</v>
+      </c>
+      <c r="P206" t="n">
+        <v>0.3120002135731486</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>0.0557662917993252</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0.9563749362175612</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -28014,6 +32171,23 @@
       <c r="M207" t="n">
         <v>3.321374254253625e-91</v>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O207" t="n">
+        <v>0.7886304625090502</v>
+      </c>
+      <c r="P207" t="n">
+        <v>-0.643263689401985</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>-0.1543608960088873</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0.7886304625090502</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -28063,6 +32237,23 @@
       <c r="M208" t="n">
         <v>1.780481063286705e-91</v>
       </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O208" t="n">
+        <v>0.7886560730577211</v>
+      </c>
+      <c r="P208" t="n">
+        <v>-0.6818888135139854</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>-0.1928946411484429</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0.7886560730577211</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -28112,6 +32303,23 @@
       <c r="M209" t="n">
         <v>7.538457257269117e-94</v>
       </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O209" t="n">
+        <v>0.7876054467653272</v>
+      </c>
+      <c r="P209" t="n">
+        <v>0.6680439888309185</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>0.1594491104648725</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0.7876054467653272</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -28161,6 +32369,23 @@
       <c r="M210" t="n">
         <v>6.420543889387796e-92</v>
       </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O210" t="n">
+        <v>0.7885344928461661</v>
+      </c>
+      <c r="P210" t="n">
+        <v>-0.6291323789685822</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>-0.136546738131099</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0.7885344928461661</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -28210,6 +32435,23 @@
       <c r="M211" t="n">
         <v>6.207618874145975e-96</v>
       </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O211" t="n">
+        <v>0.7885905210051348</v>
+      </c>
+      <c r="P211" t="n">
+        <v>0.5800892969999997</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>0.059788609714373</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0.7885905210051348</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -28259,6 +32501,23 @@
       <c r="M212" t="n">
         <v>4.136064233779799e-91</v>
       </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O212" t="n">
+        <v>0.7530691528484517</v>
+      </c>
+      <c r="P212" t="n">
+        <v>-0.5240131093964958</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>0.0804730807476351</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0.7530691528484517</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -28308,6 +32567,23 @@
       <c r="M213" t="n">
         <v>6.529092564685256e-94</v>
       </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O213" t="n">
+        <v>0.7704961873014814</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0.738705844880779</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>0.2345751595111507</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0.7704961873014814</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -28357,6 +32633,23 @@
       <c r="M214" t="n">
         <v>1.134367451915811e-93</v>
       </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O214" t="n">
+        <v>0.7885814780399198</v>
+      </c>
+      <c r="P214" t="n">
+        <v>-0.6795423856242575</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>-0.19620502335991</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0.7885814780399198</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -28406,6 +32699,23 @@
       <c r="M215" t="n">
         <v>2.077714323588818e-100</v>
       </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O215" t="n">
+        <v>0.7045047006420576</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0.6525488304908394</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>0.0187386413971262</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0.7045047006420576</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -28455,6 +32765,23 @@
       <c r="M216" t="n">
         <v>2.963446707494612e-91</v>
       </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O216" t="n">
+        <v>0.7822988139470913</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0.6487866686838873</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>0.1309375426605306</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0.7822988139470913</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -28504,6 +32831,23 @@
       <c r="M217" t="n">
         <v>4.434989673619348e-91</v>
       </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O217" t="n">
+        <v>0.7721114055696225</v>
+      </c>
+      <c r="P217" t="n">
+        <v>0.7278540974475949</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>0.2257934157804421</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0.7721114055696225</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -28553,6 +32897,23 @@
       <c r="M218" t="n">
         <v>2.220219195884721e-97</v>
       </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O218" t="n">
+        <v>0.7882343624089243</v>
+      </c>
+      <c r="P218" t="n">
+        <v>0.6376623101627925</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>0.1264355855958535</v>
+      </c>
+      <c r="R218" t="n">
+        <v>0.7882343624089243</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -28602,6 +32963,23 @@
       <c r="M219" t="n">
         <v>1.078301600897916e-91</v>
       </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O219" t="n">
+        <v>0.7834205944983624</v>
+      </c>
+      <c r="P219" t="n">
+        <v>0.6247067539181179</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>0.0946849762514939</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0.7834205944983624</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -28651,6 +33029,23 @@
       <c r="M220" t="n">
         <v>4.11958246167813e-92</v>
       </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O220" t="n">
+        <v>0.7885529054701041</v>
+      </c>
+      <c r="P220" t="n">
+        <v>0.6077821761824992</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>0.08566546515457921</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0.7885529054701041</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -28700,6 +33095,23 @@
       <c r="M221" t="n">
         <v>1.458120317707115e-91</v>
       </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O221" t="n">
+        <v>0.7879189084904449</v>
+      </c>
+      <c r="P221" t="n">
+        <v>-0.6087825462108719</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>-0.0989382392343006</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0.7879189084904449</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -28749,6 +33161,23 @@
       <c r="M222" t="n">
         <v>8.090535855959275e-92</v>
       </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O222" t="n">
+        <v>0.7704433972933975</v>
+      </c>
+      <c r="P222" t="n">
+        <v>-0.4783516539947609</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>0.1055086639799883</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0.7704433972933975</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -28798,6 +33227,23 @@
       <c r="M223" t="n">
         <v>1.417331045409837e-83</v>
       </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O223" t="n">
+        <v>0.5623705108752195</v>
+      </c>
+      <c r="P223" t="n">
+        <v>-0.7279911910532595</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>0.1064444080086876</v>
+      </c>
+      <c r="R223" t="n">
+        <v>0.7279911910532595</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -28847,6 +33293,23 @@
       <c r="M224" t="n">
         <v>8.481293101190922e-82</v>
       </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O224" t="n">
+        <v>0.5672380964927605</v>
+      </c>
+      <c r="P224" t="n">
+        <v>0.8678343885365564</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>0.1097233286695126</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0.8678343885365564</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -28896,6 +33359,23 @@
       <c r="M225" t="n">
         <v>6.207618874145975e-96</v>
       </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O225" t="n">
+        <v>0.7880193086851384</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0.6625578245024563</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>0.1623051612807904</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0.7880193086851384</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -28945,6 +33425,23 @@
       <c r="M226" t="n">
         <v>1.321123727842603e-83</v>
       </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O226" t="n">
+        <v>0.8871405787940625</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0.547767966035843</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>0.1582809888407365</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0.8871405787940625</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -28994,6 +33491,23 @@
       <c r="M227" t="n">
         <v>1.47878016519314e-101</v>
       </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O227" t="n">
+        <v>0.7939646695764057</v>
+      </c>
+      <c r="P227" t="n">
+        <v>0.8725501456359352</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>0.509387873629473</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0.8725501456359352</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -29043,6 +33557,23 @@
       <c r="M228" t="n">
         <v>8.176480896380411e-83</v>
       </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O228" t="n">
+        <v>0.8495051044940175</v>
+      </c>
+      <c r="P228" t="n">
+        <v>-0.5915767187809906</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>-0.1211458690018752</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0.8495051044940175</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -29092,6 +33623,23 @@
       <c r="M229" t="n">
         <v>1.006142647380408e-85</v>
       </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O229" t="n">
+        <v>0.7424618550976479</v>
+      </c>
+      <c r="P229" t="n">
+        <v>-0.5944331751674949</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>0.0042236727194998</v>
+      </c>
+      <c r="R229" t="n">
+        <v>0.7424618550976479</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -29141,6 +33689,23 @@
       <c r="M230" t="n">
         <v>5.487123583040718e-86</v>
       </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O230" t="n">
+        <v>0.7141215292439004</v>
+      </c>
+      <c r="P230" t="n">
+        <v>0.9103847692835414</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>0.4252767671732745</v>
+      </c>
+      <c r="R230" t="n">
+        <v>0.9103847692835414</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -29190,6 +33755,23 @@
       <c r="M231" t="n">
         <v>6.401851194528176e-10</v>
       </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O231" t="n">
+        <v>0.7466064177501371</v>
+      </c>
+      <c r="P231" t="n">
+        <v>0.912470384068828</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>0.465276688538547</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0.912470384068828</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -29239,6 +33821,23 @@
       <c r="M232" t="n">
         <v>4.784035766639741e-10</v>
       </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O232" t="n">
+        <v>0.9134026644793852</v>
+      </c>
+      <c r="P232" t="n">
+        <v>0.7505380021650342</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>0.4702430089094658</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0.9134026644793852</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -29288,6 +33887,23 @@
       <c r="M233" t="n">
         <v>1.082001196964919e-86</v>
       </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O233" t="n">
+        <v>0.78998067728378</v>
+      </c>
+      <c r="P233" t="n">
+        <v>-0.5936546971621514</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>-0.0690312114772455</v>
+      </c>
+      <c r="R233" t="n">
+        <v>0.78998067728378</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -29337,6 +33953,23 @@
       <c r="M234" t="n">
         <v>3.550542854611554e-82</v>
       </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O234" t="n">
+        <v>0.7737851871793904</v>
+      </c>
+      <c r="P234" t="n">
+        <v>0.6496747036179144</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>0.0670206546786213</v>
+      </c>
+      <c r="R234" t="n">
+        <v>0.7737851871793904</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -29386,6 +34019,23 @@
       <c r="M235" t="n">
         <v>5.448607947549419e-81</v>
       </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O235" t="n">
+        <v>0.7599205540108631</v>
+      </c>
+      <c r="P235" t="n">
+        <v>0.7666180126148324</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>0.2241688968165111</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0.7666180126148324</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -29435,6 +34085,23 @@
       <c r="M236" t="n">
         <v>3.289563079262601e-81</v>
       </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O236" t="n">
+        <v>0.740873887190571</v>
+      </c>
+      <c r="P236" t="n">
+        <v>0.7721768989310063</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>0.2002067256515767</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0.7721768989310063</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -29484,6 +34151,23 @@
       <c r="M237" t="n">
         <v>2.759109177166653e-101</v>
       </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="O237" t="n">
+        <v>0.6595918066885046</v>
+      </c>
+      <c r="P237" t="n">
+        <v>-0.6195549708827045</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>0.08903740294332579</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0.6595918066885046</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -29532,6 +34216,23 @@
       </c>
       <c r="M238" t="n">
         <v>7.571298904115574e-95</v>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="O238" t="n">
+        <v>0.4302905495189969</v>
+      </c>
+      <c r="P238" t="n">
+        <v>0.9660765692799692</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>0.2401571584152761</v>
+      </c>
+      <c r="R238" t="n">
+        <v>0.9660765692799692</v>
       </c>
     </row>
   </sheetData>
@@ -52564,7 +57265,7 @@
     <row r="1" ht="90" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supplementary Table 7. Candidate conserved markers: synergistic pairs identified independently in &gt;= 2 cohorts with the same diagnosis (only inflammatory bowel disease, HallAB_2017 and NielsenHB_2014, met this criterion). Pairs were matched irrespective of orientation; orientation_per_cohort gives the (base -&gt; contributing) direction reported in each cohort and same_orientation_in_all_cohorts whether it agrees. IG values are means over the cohorts.</t>
+          <t>Supplementary Table 7. Candidate conserved markers: synergistic pairs identified independently in &gt;= 2 cohorts with the same diagnosis (only inflammatory bowel disease, HallAB_2017 and NielsenHB_2014, met this criterion). Pairs were matched irrespective of orientation; orientation_per_cohort gives the (base -&gt; contributing) direction reported in each cohort and same_orientation_in_all_cohorts whether it agrees. IG values are means over the cohorts; mean_ig_gain_pct is the IG added by the contributing feature relative to the 1D IG of the base feature and is very large when that IG is close to zero (Blautia hydrogenotrophica in HallAB_2017: 0.014).</t>
         </is>
       </c>
     </row>
